--- a/nli-report.xlsx
+++ b/nli-report.xlsx
@@ -10212,23 +10212,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>פוליני (מחוז יורה, צרפת)</t>
+          <t>פוליני (מחוז מרת ומוזל, צרפת)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>פוליני (מחוז מרת ומוזל, צרפת)</t>
+          <t>פוליני (מחוז יורה, צרפת)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>לבדיקה: הרשומה הנכנסת היא Pulligny, ולפי ויקינתונים (Q1099419) היא במחוז מרת ומוזל — ואילו ההצעה מייחסת אותה ליורה. ייתכן ששני הצדדים הוחלפו. יש לאשר לפני שליחה.</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>

--- a/nli-report.xlsx
+++ b/nli-report.xlsx
@@ -13,22 +13,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="034 פגום" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מזהה ויקינתונים" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כותרת לשני מקומות" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="איות הכותרת" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תיקון הכותרת" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="זהות הכותרת" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כפילות ברשומות" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="בודדות" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הסברים" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הסברים" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'אפס שנשמט'!$A$1:$J$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'קואורדינטות שגויות'!$A$1:$M$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'034 פגום'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'מזהה ויקינתונים'!$A$1:$K$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'מזהה ויקינתונים'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'כותרת לשני מקומות'!$A$1:$M$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'איות הכותרת'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'תיקון הכותרת'!$A$1:$G$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'זהות הכותרת'!$A$1:$G$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'כפילות ברשומות'!$A$1:$J$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'בודדות'!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -573,7 +571,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">    איות הכותרת — 3 שורות — שגיאה באיות הכותרת העברית</t>
+          <t xml:space="preserve">    תיקון הכותרת — 4 שורות — שגיאה בכותרת עצמה</t>
         </is>
       </c>
     </row>
@@ -592,24 +590,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    בודדות — 1 שורות — תקלות בודדות</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>כל שורה עברה סקירה ידנית. עמודת "הערת הסוקר" נושאת את הממצא</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
-        <is>
-          <t>כל שורה עברה סקירה ידנית. עמודת "הערת הסוקר" נושאת את הממצא</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
         <is>
           <t>כפי שנרשם בעת הסקירה.</t>
         </is>
@@ -626,93 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>כותרת עברית</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>כותרת לטינית</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>מזהה NLI</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>הערת הסוקר</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>נקודת NLI</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>נקודת כימה</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>קישור לרשומה</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>North Huntingdon (Pa. : Township)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>987007562247105171</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>הסוגר הסופי חסר בכותרת.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007562247105171</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -954,22 +859,22 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>איות הכותרת</t>
+          <t>תיקון הכותרת</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>שגיאה באיות הכותרת העברית</t>
+          <t>שגיאה בכותרת עצמה</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>כאן אין עמימות ואין שני מקומות — פשוט האיות העברי של הכותרת שגוי, או שהכותרת מעלה שאלה של זהות. אלה ממצאים שעלו אגב בדיקות אחרות ונרשמו במהלך הסקירה.</t>
+          <t>כאן אין עמימות ואין שני מקומות — הכותרת עצמה פגומה: איות עברי שגוי, סוגר שלא נסגר, או שאלה של זהות. אלה ממצאים שעלו אגב בדיקות אחרות ונרשמו במהלך הסקירה, ולכל אחד מהם תיקון קונקרטי.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>לתקן את האיות לפי העמודה "האיות המוצע", או — במקרה של שטרסבורג — להכריע בשאלה שבעמודת ההסבר.</t>
+          <t>לתקן את הכותרת לפי העמודה "הצורה המוצעת", או — במקרה של שטרסבורג — להכריע בשאלה שבעמודת ההסבר.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1054,43 +959,6 @@
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>כל שורה נושאת את שני המזהים ואת שתי הכותרות.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>בודדות</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>תקלות בודדות</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>מקרים שאינם מצטרפים לתבנית — תקלה בשם הערבי, סוגר שלא נסגר בכותרת, סוגריים שנכנסו להפניה. כל שורה עומדת בזכות עצמה, וההערה שלצדה אומרת מה נמצא.</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>לקרוא את ההערה בכל שורה ולתקן בהתאם.</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>אלה מקרים שעלו במהלך סקירת קטגוריות אחרות. חלקם הוכרעו בהרצה מוקדמת יותר, והנתונים שלהם נשלפו מחדש מ־Alma OAI לצורך הדוח הזה.</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>עמודת "הערה" היא הממצא עצמו.</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9305,8 +9173,10 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="52" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9357,10 +9227,20 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
+          <t>ממצא נוסף</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>פירוט הממצא הנוסף</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
           <t>הערת הסוקר</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>קישור לרשומה</t>
         </is>
@@ -9412,10 +9292,20 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>שם ערבי משובש</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>הכותרת הערבית ברשומה היא "لوخفيت︠س︡ي︠ي︠ي︠ي︠ي︠ي (أوكرانيا)" — האות ي חוזרת שמונה פעמים. מקור התקלה בתעתיק: הצורה הלטינית Lokhvyt︠s︡i︠a︡ משתמשת בסימני חיבור (U+FE20/U+FE21) כדי לקשור t͡s ו־i͡a, וההמרה לערבית התייחסה לכל חצי סימן כאל אות ולכן שכפלה את ي. הצורה המוצעת: "لوخفيتسيا (أوكرانيا)". זו תקלה בודדת — אחת מתוך 1,188 כותרות ערביות שנבדקו.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>בעיה בשם הערבי</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007562429505171</t>
         </is>
@@ -9466,7 +9356,9 @@
         <v>2797.7</v>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007543674705171</t>
         </is>
@@ -9516,12 +9408,14 @@
       <c r="I4" t="n">
         <v>104.5</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>אלה הם שני מקומות שונים: העיר וההר. אם הכוונה לעיר, הויקידאטה הוא Q651583 והשם: הויקידאטה והקואורדינטות הנוכחיות ב-nli הן לא של etters-berg אלא של ettersburg הישוב. אם הכוונה היא להר, ממליצה לשנות את השם לאטרס-ברג (גרמניה: הר) והויקידאטה הוא  Q31547753</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007561549805171</t>
         </is>
@@ -9572,7 +9466,9 @@
         <v>54.8</v>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007546333605171</t>
         </is>
@@ -9619,7 +9515,9 @@
         <v>149.4</v>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007284646705171</t>
         </is>
@@ -9670,7 +9568,9 @@
         <v>852.1</v>
       </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007564769205171</t>
         </is>
@@ -9721,7 +9621,9 @@
         <v>726.9</v>
       </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987011433524905171</t>
         </is>
@@ -9768,14 +9670,16 @@
         <v>141.3</v>
       </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007545173905171</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K9"/>
+  <autoFilter ref="A1:M9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10283,7 +10187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10313,12 +10217,12 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>האיות ברשומה</t>
+          <t>הצורה ברשומה</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>האיות המוצע</t>
+          <t>הצורה המוצעת</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -10439,8 +10343,41 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>North Huntingdon (Pa. : Township)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>987007562247105171</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>North Huntingdon (Pa. : Township</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>North Huntingdon (Pa. : Township)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>הסוגר הסופי חסר בכותרת.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007562247105171</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/nli-report.xlsx
+++ b/nli-report.xlsx
@@ -12,10 +12,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="קואורדינטות שגויות" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="034 פגום" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מזהה ויקינתונים" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כותרת לשני מקומות" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תיקון הכותרת" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="זהות הכותרת" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כפילות ברשומות" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תיקון הכותרת" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="זהות הכותרת" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כפילות ברשומות" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="כותרת לשני מקומות" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הסברים" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
@@ -23,10 +23,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'קואורדינטות שגויות'!$A$1:$M$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'034 פגום'!$A$1:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'מזהה ויקינתונים'!$A$1:$M$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'כותרת לשני מקומות'!$A$1:$M$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'תיקון הכותרת'!$A$1:$G$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'זהות הכותרת'!$A$1:$G$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'כפילות ברשומות'!$A$1:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'תיקון הכותרת'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'זהות הכותרת'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'כפילות ברשומות'!$A$1:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'כותרת לשני מקומות'!$A$1:$M$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -461,7 +461,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>דוח שגיאות ברשומות רשות של מקומות — אוסף כימה</t>
+          <t>דוח שגיאות ברשומות זהות של מקומות — אוסף כימה</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>נוצר: 2026-09-22</t>
+          <t>עודכן לאחרונה: 2026-09-22</t>
         </is>
       </c>
     </row>
@@ -564,28 +564,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">    כותרת לשני מקומות — 8 שורות — כותרת עברית אחת לשני מקומות</t>
+          <t xml:space="preserve">    תיקון הכותרת — 4 שורות — שגיאה בכותרת עצמה</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">    תיקון הכותרת — 4 שורות — שגיאה בכותרת עצמה</t>
+          <t xml:space="preserve">    זהות הכותרת — 4 שורות — הכותרת העברית שייכת לרשומה אחרת</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    זהות הכותרת — 4 שורות — הכותרת העברית שייכת לרשומה אחרת</t>
+          <t xml:space="preserve">    כפילות ברשומות — 6 שורות — שתי רשומות לאותו מקום</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">    כפילות ברשומות — 6 שורות — שתי רשומות רשות לאותו מקום</t>
+          <t xml:space="preserve">    כותרת לשני מקומות — 8 שורות — כותרת עברית אחת לשני מקומות</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>לתקן את ערכי 034 לפי העמודה "הערך המתוקן". זה תיקון מכני: הערך הנכון נגזר מן הערך הקיים בהוספת האפס החסר, ואינו דורש הכרעה עורכית באף אחד מן המקרים.</t>
+          <t>לתקן את ערכי 034 לפי העמודה "הערך המתוקן". זה תיקון מכני: הערך הנכון נגזר מן הערך הקיים בהוספת האפס החסר, ואינו מצריך החלטה של מחלקת הקטלוג באף אחד מן המקרים.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -817,148 +817,148 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>heb-homonym</t>
+          <t>heb-spelling</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>כותרת לשני מקומות</t>
+          <t>תיקון הכותרת</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>כותרת עברית אחת לשני מקומות</t>
+          <t>שגיאה בכותרת עצמה</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>שתי רשומות רשות נפרדות — שני מקומות ממשיים ושונים — נושאות בדיוק את אותה כותרת בעברית, אף שהשם הלטיני מבדיל ביניהן. התעתיק לעברית מאבד את ההבחנה: Ehningen ו־Eningen unter Achalm נעשים שניהם "אנינגן (גרמניה)", Lüben ו־Lübben שניהם "לובן (גרמניה)". התוצאה היא שאי אפשר להפנות לאחת מהן בעברית בלי להפנות גם לשנייה.</t>
+          <t>כאן אין עמימות ואין שני מקומות — הכותרת עצמה פגומה: איות עברי שגוי, סוגר שלא נסגר, או שאלה של זהות. אלה ממצאים שעלו אגב בדיקות אחרות ונרשמו במהלך הסקירה, ולכל אחד מהם תיקון קונקרטי.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>להוסיף מבחין לכותרת העברית של כל אחד מן הצדדים. העמודות "הצעה לרשומה הנכנסת" ו"הצעה לרשומה הקיימת" נושאות הצעה קונקרטית לכל צד. ההצעות המסומנות "טיוטה" הן הצעות שלנו ולא הכרעה — הן נסמכות על החלוקה המנהלית בוויקינתונים, ואנו מבקשים את דעתכם עליהן.</t>
+          <t>לתקן את הכותרת לפי העמודה "הצורה המוצעת", או — במקרה של שטרסבורג — להכריע בשאלה שבעמודת ההסבר.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>המקרים אותרו בהשוואת הכותרות העבריות בין הרשומה הנכנסת ובין הרשומה שכבר מחזיקה את אותה כותרת. לכל זוג בדקנו את השם הלטיני, את מזהה הוויקינתונים ואת הקואורדינטות, כדי לוודא שמדובר בשני מקומות ולא בכפילות. שמות המחוזות בהצעות לקוחים מתוויות ויקינתונים בעברית, לא מתעתיק שלנו.</t>
+          <t>כל מקרה נבדק מול השם הלטיני ברשומה ומול ויקינתונים. אלה מקרים בודדים שנרשמו ידנית, לא תוצר של סיווג אוטומטי.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>עמודת "מרחק" מראה כמה רחוקים המקומות זה מזה — עדות לכך שאינם אותו מקום. עמודת "נימוק ההצעה" מסבירה על מה נשענת כל טיוטה.</t>
+          <t>עמודת "האיות ברשומה" מול "האיות המוצע", וההסבר שלצדן.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>heb-spelling</t>
+          <t>heb-identity</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>תיקון הכותרת</t>
+          <t>זהות הכותרת</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>שגיאה בכותרת עצמה</t>
+          <t>הכותרת העברית שייכת לרשומה אחרת</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>כאן אין עמימות ואין שני מקומות — הכותרת עצמה פגומה: איות עברי שגוי, סוגר שלא נסגר, או שאלה של זהות. אלה ממצאים שעלו אגב בדיקות אחרות ונרשמו במהלך הסקירה, ולכל אחד מהם תיקון קונקרטי.</t>
+          <t>מקרים שבהם הבעיה אינה באיות אלא בשיוך: כותרת עברית שיושבת על הרשומה הלא נכונה, או שתי רשומות שהן למעשה מקום אחד ויש לאחדן. אלה אינם מקרים שדורשים מבחין — הם דורשים הכרעה מה הרשומה מתארת.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>לתקן את הכותרת לפי העמודה "הצורה המוצעת", או — במקרה של שטרסבורג — להכריע בשאלה שבעמודת ההסבר.</t>
+          <t>לבדוק כל מקרה לגופו לפי ההערה שלצדו: לאחד את הרשומות, או להעביר את הכותרת העברית לרשומה שאליה היא שייכת.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>כל מקרה נבדק מול השם הלטיני ברשומה ומול ויקינתונים. אלה מקרים בודדים שנרשמו ידנית, לא תוצר של סיווג אוטומטי.</t>
+          <t>אותרו במהלך סקירת הכפילויות ואומתו מול MARC מ־Alma OAI.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>עמודת "האיות ברשומה" מול "האיות המוצע", וההסבר שלצדן.</t>
+          <t>עמודת "הערת הסוקר" נושאת את הממצא המלא לכל שורה.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>heb-identity</t>
+          <t>duplicate-records</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>זהות הכותרת</t>
+          <t>כפילות ברשומות</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>הכותרת העברית שייכת לרשומה אחרת</t>
+          <t>שתי רשומות לאותו מקום</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>מקרים שבהם הבעיה אינה באיות אלא בשיוך: כותרת עברית שיושבת על הרשומה הלא נכונה, או שתי רשומות שהן למעשה מקום אחד ויש לאחדן. אלה אינם מקרים שדורשים מבחין — הם דורשים הכרעה מה הרשומה מתארת.</t>
+          <t>שתי רשומות זהות־מקום נפרדות ב־NLI מתארות מקום אחד. בחלק מן המקרים העדות היא מזהה ויקינתונים זהה בשתיהן; באחרים אחת הכותרות היא שם היסטורי של האחרת (טולבוחין ודובריץ׳). זו אינה שאלה של איות עברי אלא של זהות הרשומה: הזהות כפולה.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>לבדוק כל מקרה לגופו לפי ההערה שלצדו: לאחד את הרשומות, או להעביר את הכותרת העברית לרשומה שאליה היא שייכת.</t>
+          <t>לבדוק את הזוגות ולמזג את הרשומות, או להסביר מה מבדיל ביניהן אם ההפרדה מכוונת.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>אותרו במהלך סקירת הכפילויות ואומתו מול MARC מ־Alma OAI.</t>
+          <t>הזוגות אותרו לפי מזהה ויקינתונים משותף ולפי הודעות הכפילות של ההרצה השבועית, ואומתו אחת אחת מול MARC מ־Alma OAI.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>עמודת "הערת הסוקר" נושאת את הממצא המלא לכל שורה.</t>
+          <t>כל שורה נושאת את שני המזהים ואת שתי הכותרות.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>duplicate-records</t>
+          <t>heb-homonym</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>כפילות ברשומות</t>
+          <t>כותרת לשני מקומות</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>שתי רשומות רשות לאותו מקום</t>
+          <t>כותרת עברית אחת לשני מקומות</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>שתי רשומות רשות נפרדות ב־NLI מתארות מקום אחד. בחלק מן המקרים העדות היא מזהה ויקינתונים זהה בשתיהן; באחרים אחת הכותרות היא שם היסטורי של האחרת (טולבוחין ודובריץ׳). זו אינה שאלה של איות עברי אלא של זהות הרשומה: הרשות כפולה.</t>
+          <t>שתי רשומות זהות־מקום נפרדות — שני מקומות ממשיים ושונים — נושאות בדיוק את אותה כותרת בעברית, אף שהשם הלטיני מבדיל ביניהן. התעתיק לעברית מאבד את ההבחנה: Ehningen ו־Eningen unter Achalm נעשים שניהם "אנינגן (גרמניה)", Lüben ו־Lübben שניהם "לובן (גרמניה)".</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>לבדוק את הזוגות ולמזג את הרשומות, או להסביר מה מבדיל ביניהן אם ההפרדה מכוונת.</t>
+          <t>להוסיף מבחין לכותרת העברית של כל אחד מן הצדדים. העמודות "הצעה לרשומה הנכנסת" ו"הצעה לרשומה הקיימת" נושאות הצעה קונקרטית לכל צד. ההצעות המסומנות "טיוטה" הן הצעות שלנו ולא הכרעה — הן נסמכות על החלוקה המנהלית בוויקינתונים, ואנו מבקשים את דעתכם עליהן.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>הזוגות אותרו לפי מזהה ויקינתונים משותף ולפי הודעות הכפילות של ההרצה השבועית, ואומתו אחת אחת מול MARC מ־Alma OAI.</t>
+          <t>המקרים אותרו בהשוואת הכותרות העבריות בין הרשומה הנכנסת ובין הרשומה שכבר מחזיקה את אותה כותרת. לכל זוג בדקנו את השם הלטיני, את מזהה הוויקינתונים ואת הקואורדינטות, כדי לוודא שמדובר בשני מקומות ולא בכפילות. שמות המחוזות בהצעות לקוחים מתוויות ויקינתונים בעברית, לא מתעתיק שלנו.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>כל שורה נושאת את שני המזהים ואת שתי הכותרות.</t>
+          <t>עמודת "מרחק" מראה כמה רחוקים המקומות זה מזה — עדות לכך שאינם אותו מקום. עמודת "נימוק ההצעה" מסבירה על מה נשענת כל טיוטה.</t>
         </is>
       </c>
     </row>
@@ -9690,503 +9690,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="52" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>הכותרת העברית המשותפת</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>מעמד ההצעה</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>הרשומה הנכנסת (לטינית)</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>מזהה NLI</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>הצעה לרשומה הנכנסת</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>הרשומה הקיימת (לטינית)</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>מזהה הרשומה הקיימת</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>הצעה לרשומה הקיימת</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>מרחק (ק״מ)</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>נימוק ההצעה</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>לבדיקה לפני שליחה</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>הערת הסוקר</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>קישור לרשומה</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>הוכשטטן (גרמניה)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>טיוטה</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Hochstätten (Germany)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>987011060395805171</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>הוכשטטן (מחוז באד קרויצנאך, גרמניה)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Hochstetten (Germany)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>987007467698905171</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>הוכשטטן (גרמניה)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>שתי רשומות שונות: Hochstätten שבמחוז באד קרויצנאך, ו־Hochstetten באיות אחר. ההצעה מוסיפה את המחוז לרשומה הנכנסת; יש לאשר מהי הרשומה השנייה לפני שמציעים לה מבחין.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987011060395805171</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>קאבה (הונגריה)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Kaba (Hungary)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>987007562214205171</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>קאבה (היידו-ביהר, הונגריה)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Káva (Hungary)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>987007373278105171</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>קאבה (פשט, הונגריה)</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>127.4</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007562214205171</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>אנינגן (גרמניה)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>טיוטה</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ehningen (Germany)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>987007494092005171</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>אנינגן (מחוז בבלינגן, גרמניה)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Eningen unter Achalm (Germany)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>987007557723505171</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>אנינגן אונטר אכלם (מחוז רויטלינגן, גרמניה)</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>שני יישובים שונים במרחק 31 ק״מ: Ehningen שבמחוז בבלינגן (Q314758) ו־Eningen unter Achalm שבמחוז רויטלינגן (Q81423). שמות המחוזות לקוחים מתוויות ויקינתונים בעברית.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007494092005171</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>צ'רנייב (אוקראינה)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>טיוטה</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Cherniïv (Ukraine)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>987007545176905171</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>צ'רנייב (מחוז איוונו-פרנקיבסק, אוקראינה)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Chernihiv (Ukraine)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>987007566754005171</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>צ'רניהיב (אוקראינה)</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>552.8</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>כאן לא די במבחין: המרחק 553 ק״מ, והרשומה השנייה היא צ׳רניהיב — בירת המחוז (Q157053), שהתעתיק העברי המקובל לה בוויקינתונים הוא "צ׳רניהיב" ולא "צ׳רנייב". כלומר אחת הכותרות שגויה ולא רק עמומה.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007545176905171</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>לובן (גרמניה)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>טיוטה</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Lüben (Germany)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>987007494367505171</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>לובין (מחוז דולנוסלונסקיה, פולין)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lübben (Germany)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>987007473617305171</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>לובן (מחוז דאמה-שפרוואלד, גרמניה)</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>170</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>לפי הערת הסוקר, הרשומה הנכנסת היא Lubin שבפולין — השם העכשווי — ו־Lüben/Lueben הם וריאנטים היסטוריים שלה. הרשומה השנייה היא Lübben שבברנדנבורג (Q584815). שני מקומות שונים ב־170 ק״מ.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>צריך להיות Lubin (Dolnośląskie, Poland)  - השם העכשווי. luben כמו גם Lueben צריכים להיות וריאנטים.</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007494367505171</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>מריון (פנסילבניה)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Merion (Pa.)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>987007559599105171</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>מריון סטיישן (פנסילבניה)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>מריון (פנסילבניה)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>לצורך דיסאמביגואציה של השם בעברית. לחלופין, אפשר להוסיף מחוזות (מונטגומרי, פרנקלין), אם כי מריון סטיישן הוא השם המוכר יותר.</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007559599105171</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>פוליני (צרפת)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Pulligny (France)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>987010489292905171</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>פוליני (מחוז מרת ומוזל, צרפת)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>פוליני (מחוז יורה, צרפת)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987010489292905171</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>אופנהיים (גרמניה)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Uffenheim (Germany)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>987011252608705171</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>אופנהיים (בוואריה, גרמניה)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>אופנהיים (ריינלנד-פפאלץ, גרמניה)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987011252608705171</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:M9"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10382,7 +9885,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10587,7 +10090,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10922,4 +10425,501 @@
   <autoFilter ref="A1:J7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>הכותרת העברית המשותפת</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>מעמד ההצעה</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>הרשומה הנכנסת (לטינית)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>מזהה NLI</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>הצעה לרשומה הנכנסת</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>הרשומה הקיימת (לטינית)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>מזהה הרשומה הקיימת</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>הצעה לרשומה הקיימת</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>מרחק (ק״מ)</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>נימוק ההצעה</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>לבדיקה לפני שליחה</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>הערת הסוקר</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>קישור לרשומה</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>הוכשטטן (גרמניה)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>טיוטה</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hochstätten (Germany)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>987011060395805171</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>הוכשטטן (מחוז באד קרויצנאך, גרמניה)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Hochstetten (Germany)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>987007467698905171</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>הוכשטטן (גרמניה)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>שתי רשומות שונות: Hochstätten שבמחוז באד קרויצנאך, ו־Hochstetten באיות אחר. ההצעה מוסיפה את המחוז לרשומה הנכנסת; יש לאשר מהי הרשומה השנייה לפני שמציעים לה מבחין.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987011060395805171</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>קאבה (הונגריה)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Kaba (Hungary)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>987007562214205171</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>קאבה (היידו-ביהר, הונגריה)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Káva (Hungary)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>987007373278105171</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>קאבה (פשט, הונגריה)</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007562214205171</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>אנינגן (גרמניה)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>טיוטה</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ehningen (Germany)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>987007494092005171</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>אנינגן (מחוז בבלינגן, גרמניה)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Eningen unter Achalm (Germany)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>987007557723505171</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>אנינגן אונטר אכלם (מחוז רויטלינגן, גרמניה)</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>שני יישובים שונים במרחק 31 ק״מ: Ehningen שבמחוז בבלינגן (Q314758) ו־Eningen unter Achalm שבמחוז רויטלינגן (Q81423). שמות המחוזות לקוחים מתוויות ויקינתונים בעברית.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007494092005171</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>צ'רנייב (אוקראינה)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>טיוטה</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cherniïv (Ukraine)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>987007545176905171</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>צ'רנייב (מחוז איוונו-פרנקיבסק, אוקראינה)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Chernihiv (Ukraine)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>987007566754005171</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>צ'רניהיב (אוקראינה)</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>552.8</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>כאן לא די במבחין: המרחק 553 ק״מ, והרשומה השנייה היא צ׳רניהיב — בירת המחוז (Q157053), שהתעתיק העברי המקובל לה בוויקינתונים הוא "צ׳רניהיב" ולא "צ׳רנייב". כלומר אחת הכותרות שגויה ולא רק עמומה.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007545176905171</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>לובן (גרמניה)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>טיוטה</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Lüben (Germany)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>987007494367505171</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>לובין (מחוז דולנוסלונסקיה, פולין)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lübben (Germany)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>987007473617305171</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>לובן (מחוז דאמה-שפרוואלד, גרמניה)</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>170</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>לפי הערת הסוקר, הרשומה הנכנסת היא Lubin שבפולין — השם העכשווי — ו־Lüben/Lueben הם וריאנטים היסטוריים שלה. הרשומה השנייה היא Lübben שבברנדנבורג (Q584815). שני מקומות שונים ב־170 ק״מ.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>צריך להיות Lubin (Dolnośląskie, Poland)  - השם העכשווי. luben כמו גם Lueben צריכים להיות וריאנטים.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007494367505171</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>מריון (פנסילבניה)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Merion (Pa.)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>987007559599105171</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>מריון סטיישן (פנסילבניה)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>מריון (פנסילבניה)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>לצורך דיסאמביגואציה של השם בעברית. לחלופין, אפשר להוסיף מחוזות (מונטגומרי, פרנקלין), אם כי מריון סטיישן הוא השם המוכר יותר.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007559599105171</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>פוליני (צרפת)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pulligny (France)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>987010489292905171</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>פוליני (מחוז מרת ומוזל, צרפת)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>פוליני (מחוז יורה, צרפת)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987010489292905171</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>אופנהיים (גרמניה)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Uffenheim (Germany)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>987011252608705171</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>אופנהיים (בוואריה, גרמניה)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>אופנהיים (ריינלנד-פפאלץ, גרמניה)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987011252608705171</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/nli-report.xlsx
+++ b/nli-report.xlsx
@@ -19,13 +19,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הסברים" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'אפס שנשמט'!$A$1:$J$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'קואורדינטות שגויות'!$A$1:$M$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'אפס שנשמט'!$A$1:$K$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'קואורדינטות שגויות'!$A$1:$M$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'034 פגום'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'מזהה ויקינתונים'!$A$1:$M$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'תיקון הכותרת'!$A$1:$G$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'זהות הכותרת'!$A$1:$G$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'כפילות ברשומות'!$A$1:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'מזהה ויקינתונים'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'תיקון הכותרת'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'זהות הכותרת'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'כפילות ברשומות'!$A$1:$K$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'כותרת לשני מקומות'!$A$1:$M$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +478,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>סך השורות: 183</t>
+          <t>סך השורות: 181</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">    קואורדינטות שגויות — 108 שורות — הקואורדינטות ברשומה מצביעות על מקום אחר</t>
+          <t xml:space="preserve">    קואורדינטות שגויות — 106 שורות — הקואורדינטות ברשומה מצביעות על מקום אחר</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -986,6 +986,7 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,6 +1040,11 @@
           <t>קישור לרשומה</t>
         </is>
       </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>נכלל בדוח מיום</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1085,6 +1091,11 @@
           <t>https://www.nli.org.il/he/authorities/987007473377705171</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1135,6 +1146,11 @@
           <t>https://www.nli.org.il/he/authorities/987007554800205171</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1181,6 +1197,11 @@
           <t>https://www.nli.org.il/he/authorities/987007528339905171</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1231,6 +1252,11 @@
           <t>https://www.nli.org.il/he/authorities/987007557223005171</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1281,6 +1307,11 @@
           <t>https://www.nli.org.il/he/authorities/987007515276905171</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1331,6 +1362,11 @@
           <t>https://www.nli.org.il/he/authorities/987007559817105171</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1381,6 +1417,11 @@
           <t>https://www.nli.org.il/he/authorities/987007559511105171</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1427,6 +1468,11 @@
           <t>https://www.nli.org.il/he/authorities/987007291078305171</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1477,6 +1523,11 @@
           <t>https://www.nli.org.il/he/authorities/987007552705605171</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1527,6 +1578,11 @@
           <t>https://www.nli.org.il/he/authorities/987007590336505171</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1577,6 +1633,11 @@
           <t>https://www.nli.org.il/he/authorities/987007532142005171</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1623,6 +1684,11 @@
           <t>https://www.nli.org.il/he/authorities/987007583812005171</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1673,6 +1739,11 @@
           <t>https://www.nli.org.il/he/authorities/987007590343505171</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1719,6 +1790,11 @@
           <t>https://www.nli.org.il/he/authorities/987007590337405171</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1769,6 +1845,11 @@
           <t>https://www.nli.org.il/he/authorities/987007566967205171</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1819,6 +1900,11 @@
           <t>https://www.nli.org.il/he/authorities/987007577116405171</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1869,6 +1955,11 @@
           <t>https://www.nli.org.il/he/authorities/987007566970705171</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1919,6 +2010,11 @@
           <t>https://www.nli.org.il/he/authorities/987007567077805171</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1969,6 +2065,11 @@
           <t>https://www.nli.org.il/he/authorities/987007567666505171</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2019,6 +2120,11 @@
           <t>https://www.nli.org.il/he/authorities/987007566894205171</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2069,6 +2175,11 @@
           <t>https://www.nli.org.il/he/authorities/987007564333805171</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2119,6 +2230,11 @@
           <t>https://www.nli.org.il/he/authorities/987007564586605171</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2169,6 +2285,11 @@
           <t>https://www.nli.org.il/he/authorities/987007567731305171</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2219,6 +2340,11 @@
           <t>https://www.nli.org.il/he/authorities/987007566714905171</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2269,6 +2395,11 @@
           <t>https://www.nli.org.il/he/authorities/987007566855105171</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2319,6 +2450,11 @@
           <t>https://www.nli.org.il/he/authorities/987007567118505171</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2369,6 +2505,11 @@
           <t>https://www.nli.org.il/he/authorities/987007560239705171</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2419,6 +2560,11 @@
           <t>https://www.nli.org.il/he/authorities/987007566857905171</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2469,6 +2615,11 @@
           <t>https://www.nli.org.il/he/authorities/987007562086705171</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2519,6 +2670,11 @@
           <t>https://www.nli.org.il/he/authorities/987007562351605171</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2569,6 +2725,11 @@
           <t>https://www.nli.org.il/he/authorities/987007564736505171</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2619,6 +2780,11 @@
           <t>https://www.nli.org.il/he/authorities/987007564736405171</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2669,6 +2835,11 @@
           <t>https://www.nli.org.il/he/authorities/987007564343005171</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2719,6 +2890,11 @@
           <t>https://www.nli.org.il/he/authorities/987007560069505171</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2765,6 +2941,11 @@
           <t>https://www.nli.org.il/he/authorities/987007562251505171</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2815,6 +2996,11 @@
           <t>https://www.nli.org.il/he/authorities/987007560162605171</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2865,6 +3051,11 @@
           <t>https://www.nli.org.il/he/authorities/987007560247005171</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2911,6 +3102,11 @@
           <t>https://www.nli.org.il/he/authorities/987007564445805171</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2961,6 +3157,11 @@
           <t>https://www.nli.org.il/he/authorities/987007565278505171</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3011,6 +3212,11 @@
           <t>https://www.nli.org.il/he/authorities/987007562550005171</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3061,6 +3267,11 @@
           <t>https://www.nli.org.il/he/authorities/987007564489505171</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3111,6 +3322,11 @@
           <t>https://www.nli.org.il/he/authorities/987007562209605171</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3161,6 +3377,11 @@
           <t>https://www.nli.org.il/he/authorities/987007567047105171</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3211,9 +3432,14 @@
           <t>https://www.nli.org.il/he/authorities/987007562110305171</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J45"/>
+  <autoFilter ref="A1:K45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3224,7 +3450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M109"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3237,9 +3463,9 @@
     <col hidden="1" width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="52" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3290,22 +3516,22 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>מזהה ויקינתונים נכון</t>
+          <t>GeoNames</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>GeoNames</t>
+          <t>הערת הסוקר</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>הערת הסוקר</t>
+          <t>קישור לרשומה</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>קישור לרשומה</t>
+          <t>נכלל בדוח מיום</t>
         </is>
       </c>
     </row>
@@ -3353,16 +3579,20 @@
           <t>Q2416499</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>2822902</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007507581905171</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007507581905171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -3410,161 +3640,173 @@
           <t>Q1893589</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>7532897</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007522876305171</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007522876305171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>פודהייל (פולין)</t>
+          <t>אלף האיים (אינדונזיה)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Podhale (Poland)</t>
+          <t>Thousand Islands (Indonesia)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>987007558385105171</t>
+          <t>987007290978605171</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>49.47930, 20.02910</t>
+          <t>1.07895, 117.90961</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.84401, 20.64039</t>
+          <t>-5.66290, 106.56830</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>157.9</v>
+        <v>1465.6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kima's point disagrees with NLI and with Kima's own Wikidata</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Q115155</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>8426167</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>Q10107</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5140907</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007290978605171</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007558385105171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>אלף האיים (אינדונזיה)</t>
+          <t>ביג ת'יקט (טקסס)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thousand Islands (Indonesia)</t>
+          <t>Big Thicket (Tex.)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>987007290978605171</t>
+          <t>987007534295705171</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.07895, 117.90961</t>
+          <t>31.11323, -98.43754</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-5.66290, 106.56830</t>
+          <t>30.54750, -94.34000</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1465.6</v>
+        <v>396.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Q10107</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>5140907</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>Q34696004</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4674406</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007534295705171</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007290978605171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ביג ת'יקט (טקסס)</t>
+          <t>הימרה (עיר קדומה)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Big Thicket (Tex.)</t>
+          <t>Himera (Extinct city)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>987007534295705171</t>
+          <t>987007561062905171</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>31.11323, -98.43754</t>
+          <t>37.65940, 14.10460</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30.54750, -94.34000</t>
+          <t>37.97055, 13.82221</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>396.2</v>
+        <v>42.6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3573,112 +3815,120 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Q34696004</t>
+          <t>Q1111219</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>4674406</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007561062905171</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007534295705171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>הימרה (עיר קדומה)</t>
+          <t>הרי וואסאץ' (יוטה ואיידהו)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Himera (Extinct city)</t>
+          <t>Wasatch Range (Utah and Idaho)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>987007561062905171</t>
+          <t>987007551287205171</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>37.65940, 14.10460</t>
+          <t>39.82139, -111.75972</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>37.97055, 13.82221</t>
+          <t>40.49000, -111.69611</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>42.6</v>
+        <v>74.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>river/region/range — both points lie on the feature, no real move</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Q1111219</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>Q1544388</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5549209</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007551287205171</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007561062905171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>הרי וואסאץ' (יוטה ואיידהו)</t>
+          <t>מאיר שפיה (ישראל)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wasatch Range (Utah and Idaho)</t>
+          <t>Me'ir Shfeya (Israel)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>987007551287205171</t>
+          <t>987007565185505171</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>39.82139, -111.75972</t>
+          <t>32.10197, 34.87391</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>40.49000, -111.69611</t>
+          <t>32.59034, 34.97064</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>74.5</v>
+        <v>55.1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>river/region/range — both points lie on the feature, no real move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3688,50 +3938,50 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Q1544388</t>
+          <t>Q2777355</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>5549209</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007565185505171</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007551287205171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>מאיר שפיה (ישראל)</t>
+          <t>חיילונגג'יאנג (סין)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Me'ir Shfeya (Israel)</t>
+          <t>Heilongjiang Sheng (China)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>987007565185505171</t>
+          <t>987012219373405171</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>32.10197, 34.87391</t>
+          <t>48.00000, 128.00000</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>32.59034, 34.97064</t>
+          <t>45.70700, 126.61700</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>55.1</v>
+        <v>275.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3740,55 +3990,55 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Q2777355</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987012219373405171</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007565185505171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>אתר יפתחאל (ישראל)</t>
+          <t>קאסל (גרמניה)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yiftahel Site (Israel)</t>
+          <t>Kassel (Germany)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>987007549317505171</t>
+          <t>987007564322205171</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>32.75540, 35.22770</t>
+          <t>50.20017, 9.28866</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37.92500, 29.12583</t>
+          <t>51.31578, 9.49792</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>797.6</v>
+        <v>124.9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Kima's Wikidata id points at the wrong entity</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3798,46 +4048,54 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Q4228288</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>Q2865</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2892518</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564322205171</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007549317505171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>חיילונגג'יאנג (סין)</t>
+          <t>צ'אד, אגם</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Heilongjiang Sheng (China)</t>
+          <t>Chad, Lake</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>987012219373405171</t>
+          <t>987007284803205171</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>48.00000, 128.00000</t>
+          <t>13.00000, 14.00000</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>45.70700, 126.61700</t>
+          <t>13.09926, 14.50463</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>275.8</v>
+        <v>55.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3846,47 +4104,55 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Q125309</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007284803205171</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987012219373405171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>קאסל (גרמניה)</t>
+          <t>נהר סנט מרי'ס (מישיגן ואונטריו)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kassel (Germany)</t>
+          <t>Saint Marys River (Mich. and Ont.)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>987007564322205171</t>
+          <t>987007529708805171</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>50.20017, 9.28866</t>
+          <t>46.50558, -84.61116</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>51.31578, 9.49792</t>
+          <t>45.95835, -83.89723</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>124.9</v>
+        <v>82</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3900,50 +4166,54 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Q2865</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2892518</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>Q940488</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4368319</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007529708805171</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564322205171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>צ'אד, אגם</t>
+          <t>פיניקיה</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chad, Lake</t>
+          <t>Phoenicia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>987007284803205171</t>
+          <t>987007555456905171</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13.00000, 14.00000</t>
+          <t>42.08140, -74.31310</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13.09926, 14.50463</t>
+          <t>34.11667, 35.65000</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>55.8</v>
+        <v>8944.299999999999</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3957,46 +4227,50 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Q125309</t>
+          <t>Q41642</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007555456905171</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007284803205171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>נהר סנט מרי'ס (מישיגן ואונטריו)</t>
+          <t>איי אפארסה</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Saint Marys River (Mich. and Ont.)</t>
+          <t>Éparses Islands</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>987007529708805171</t>
+          <t>987007415889605171</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>46.50558, -84.61116</t>
+          <t>-17.04333, 42.74480</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.95835, -83.89723</t>
+          <t>-22.34389, 40.36722</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>82</v>
+        <v>639.8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -4010,50 +4284,50 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Q940488</t>
+          <t>Q190571</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>4368319</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007415889605171</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007529708805171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>פיניקיה</t>
+          <t>המישורים הגדולים</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Phoenicia</t>
+          <t>Great Plains</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>987007555456905171</t>
+          <t>987007540907105171</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>42.08140, -74.31310</t>
+          <t>42.00000, -102.00000</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>34.11667, 35.65000</t>
+          <t>40.00000, -100.00000</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>8944.299999999999</v>
+        <v>278.6</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -4067,46 +4341,50 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Q41642</t>
+          <t>Q12707</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007540907105171</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007555456905171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>איי אפארסה</t>
+          <t>מאלמו (שוודיה)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Éparses Islands</t>
+          <t>Malmö (Sweden)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>987007415889605171</t>
+          <t>987007552629505171</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-17.04333, 42.74480</t>
+          <t>57.81667, 16.70000</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-22.34389, 40.36722</t>
+          <t>55.59319, 13.02142</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>639.8</v>
+        <v>333.9</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -4115,51 +4393,55 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Q190571</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2692969</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007552629505171</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007415889605171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>המישורים הגדולים</t>
+          <t>מנסטר בלאקווטר (קרי-קורק ווטררפורד, אירלנד)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Great Plains</t>
+          <t>Blackwater, River (Kerry-Cork and Waterford, Ireland)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>987007540907105171</t>
+          <t>987007554238205171</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>42.00000, -102.00000</t>
+          <t>52.19200, -9.24100</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>40.00000, -100.00000</t>
+          <t>51.94120, -7.83600</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>278.6</v>
+        <v>100</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -4173,46 +4455,50 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Q12707</t>
+          <t>Q1464482</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007554238205171</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007540907105171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>מאלמו (שוודיה)</t>
+          <t>אזור במיין (אפגניסטן)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Malmö (Sweden)</t>
+          <t>Bāmīān Region (Afghanistan)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>987007552629505171</t>
+          <t>987007282291905171</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>57.81667, 16.70000</t>
+          <t>34.69668, 67.27667</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>55.59319, 13.02142</t>
+          <t>34.81667, 67.81667</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>333.9</v>
+        <v>51.1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4226,46 +4512,46 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2692969</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007282291905171</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007552629505171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>מנסטר בלאקווטר (קרי-קורק ווטררפורד, אירלנד)</t>
+          <t>עין אל-זייתון (ישראל)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Blackwater, River (Kerry-Cork and Waterford, Ireland)</t>
+          <t>Ein al-Zeitun (Israel)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>987007554238205171</t>
+          <t>987007524670705171</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.19200, -9.24100</t>
+          <t>32.23320, 34.94609</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>51.94120, -7.83600</t>
+          <t>32.98723, 35.49155</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4279,46 +4565,50 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Q1464482</t>
+          <t>Q5349602</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007524670705171</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007554238205171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>אזור במיין (אפגניסטן)</t>
+          <t>ברוק (גרמניה)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bāmīān Region (Afghanistan)</t>
+          <t>Brück (Germany)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>987007282291905171</t>
+          <t>987007507433105171</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>34.69668, 67.27667</t>
+          <t>50.94320, 7.34129</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>34.81667, 67.81667</t>
+          <t>50.48580, 6.97096</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>51.1</v>
+        <v>57.2</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4330,44 +4620,56 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Q995940</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2943520</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007507433105171</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007282291905171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>עין אל-זייתון (ישראל)</t>
+          <t>שט אל-ערב (איראן ועיראק)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ein al-Zeitun (Israel)</t>
+          <t>Shatt al-Arab (Iraq and Iran)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>987007524670705171</t>
+          <t>987007536434705171</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>32.23320, 34.94609</t>
+          <t>29.93690, 48.60770</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>32.98723, 35.49155</t>
+          <t>31.00430, 47.44210</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>98.2</v>
+        <v>163</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4381,50 +4683,58 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Q5349602</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>Q166966</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>143160</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007536434705171</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007524670705171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ברוק (גרמניה)</t>
+          <t>אורנצ'יק (טורקיה)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Brück (Germany)</t>
+          <t>Örencik (Turkey)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>987007507433105171</t>
+          <t>987007583811505171</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>50.94320, 7.34129</t>
+          <t>37.93480, 37.71533</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>50.48580, 6.97096</t>
+          <t>38.48920, 29.89720</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>57.2</v>
+        <v>685.6</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -4434,50 +4744,58 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Q995940</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>Q4821258</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>741074</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2943520</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+          <t>יש הרבה מקומות בשם זה בטורקיה - במקרה הזה מזהה הויקידאטה לא תואם את הקואורדינטות.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007583811505171</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007507433105171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>שט אל-ערב (איראן ועיראק)</t>
+          <t>אי הפסחא</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shatt al-Arab (Iraq and Iran)</t>
+          <t>Easter Island</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>987007536434705171</t>
+          <t>987007567857705171</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>29.93690, 48.60770</t>
+          <t>-66.41667, 98.76667</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>31.00430, 47.44210</t>
+          <t>-27.11944, -109.35472</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>163</v>
+        <v>9345.6</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -4491,111 +4809,107 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Q166966</t>
+          <t>Q14452</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>143160</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007567857705171</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007536434705171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>אורנצ'יק (טורקיה)</t>
+          <t>אירופה המזרחית</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Örencik (Turkey)</t>
+          <t>Europe, Eastern</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>987007583811505171</t>
+          <t>987007560192505171</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>37.93480, 37.71533</t>
+          <t>50.82308, -1.46568</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>38.48920, 29.89720</t>
+          <t>49.00000, 31.00000</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>685.6</v>
+        <v>2314.7</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Q4821258</t>
+          <t>Q27468</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>741074</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>יש הרבה מקומות בשם זה בטורקיה - במקרה הזה מזהה הויקידאטה לא תואם את הקואורדינטות.</t>
+          <t>https://www.nli.org.il/he/authorities/987007560192505171</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007583811505171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>אי הפסחא</t>
+          <t>הרי האלפים הצרפתיים (צרפת)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Easter Island</t>
+          <t>Alps, French (France)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>987007567857705171</t>
+          <t>987007294887505171</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-66.41667, 98.76667</t>
+          <t>46.41667, 10.00000</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>-27.11944, -109.35472</t>
+          <t>44.80000, 6.50000</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>9345.6</v>
+        <v>326.2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -4604,51 +4918,51 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Q14452</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007294887505171</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567857705171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>אירופה המזרחית</t>
+          <t>איי טרמיטי (איטליה)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Europe, Eastern</t>
+          <t>Tremiti Islands (Italy)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>987007560192505171</t>
+          <t>987007541762605171</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>50.82308, -1.46568</t>
+          <t>40.11667, 15.50000</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>49.00000, 31.00000</t>
+          <t>42.11667, 15.50000</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2314.7</v>
+        <v>222.4</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -4662,46 +4976,54 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Q27468</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>Q51930</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>3165250</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007541762605171</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007560192505171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>הרי האלפים הצרפתיים (צרפת)</t>
+          <t>גרנד בנקס של ניופאונדלנד</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Alps, French (France)</t>
+          <t>Grand Banks of Newfoundland</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>987007294887505171</t>
+          <t>987007536002505171</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.41667, 10.00000</t>
+          <t>45.00000, -53.00000</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>44.80000, 6.50000</t>
+          <t>45.23694, -50.98922</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>326.2</v>
+        <v>160</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -4716,41 +5038,45 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007536002505171</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007294887505171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>איי טרמיטי (איטליה)</t>
+          <t>גלדיבולדו (טורקיה)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tremiti Islands (Italy)</t>
+          <t>Geldibuldu (Turkey)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>987007541762605171</t>
+          <t>987007537927405171</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>40.11667, 15.50000</t>
+          <t>40.18333, 32.83333</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>42.11667, 15.50000</t>
+          <t>37.72807, 38.86933</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>222.4</v>
+        <v>588.8</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -4764,50 +5090,54 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Q51930</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>3165250</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
+          <t>Q4831991</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>312116</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007537927405171</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007541762605171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>גרנד בנקס של ניופאונדלנד</t>
+          <t>גוס איילנד (שיקגו, אילינוי)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Grand Banks of Newfoundland</t>
+          <t>Goose Island (Chicago, Ill.)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>987007536002505171</t>
+          <t>987007539410905171</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.00000, -53.00000</t>
+          <t>37.12556, -89.40306</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>45.23694, -50.98922</t>
+          <t>41.90392, -87.65394</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>160</v>
+        <v>552.1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -4819,44 +5149,52 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Q5584067</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007539410905171</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007536002505171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>גלדיבולדו (טורקיה)</t>
+          <t>קמלדולי (איטליה)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Geldibuldu (Turkey)</t>
+          <t>Camaldoli (Italy)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>987007537927405171</t>
+          <t>987007550230005171</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>40.18333, 32.83333</t>
+          <t>40.85000, 14.20000</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>37.72807, 38.86933</t>
+          <t>44.42031, 8.98444</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>588.8</v>
+        <v>582.6</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -4870,103 +5208,111 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Q4831991</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>312116</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
+          <t>Q18456541</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>8953134</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007550230005171</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007537927405171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>גוס איילנד (שיקגו, אילינוי)</t>
+          <t>האבלוי (צרפת)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Goose Island (Chicago, Ill.)</t>
+          <t>Haveluy (France)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>987007539410905171</t>
+          <t>987007535425005171</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>37.12556, -89.40306</t>
+          <t>21.00000, 3.40000</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>41.90392, -87.65394</t>
+          <t>50.35289, 3.40389</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>552.1</v>
+        <v>3263.9</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>no Wikidata entity to arbitrate with</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Q5584067</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>3013637</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007535425005171</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007539410905171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>קמלדולי (איטליה)</t>
+          <t>יוכן (גרמניה)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Camaldoli (Italy)</t>
+          <t>Jüchen (Germany)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>987007550230005171</t>
+          <t>987007489333905171</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>40.85000, 14.20000</t>
+          <t>51.50000, 6.50000</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>44.42031, 8.98444</t>
+          <t>51.10111, 6.50167</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>582.6</v>
+        <v>44.4</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4980,103 +5326,111 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Q18456541</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>8953134</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
+          <t>Q255416</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>6291043</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007489333905171</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007550230005171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>האבלוי (צרפת)</t>
+          <t>מיטשלוויל (קרולינה הדרומית)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Haveluy (France)</t>
+          <t>Mitchellville (S.C.)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>987007535425005171</t>
+          <t>987007480256305171</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>21.00000, 3.40000</t>
+          <t>32.46167, -80.99222</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>50.35289, 3.40389</t>
+          <t>41.66722, -93.36028</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3263.9</v>
+        <v>1497.8</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>no Wikidata entity to arbitrate with</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Q1914731</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>3013637</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007480256305171</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007535425005171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>יוכן (גרמניה)</t>
+          <t>תל סאוואן (עיראק)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jüchen (Germany)</t>
+          <t>Sawwan, Tall (Iraq)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>987007489333905171</t>
+          <t>987007549454405171</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>51.50000, 6.50000</t>
+          <t>36.21222, 42.64972</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>51.10111, 6.50167</t>
+          <t>34.11670, 43.90000</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>44.4</v>
+        <v>259.2</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -5085,55 +5439,51 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Q255416</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>6291043</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007549454405171</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007489333905171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>מיטשלוויל (קרולינה הדרומית)</t>
+          <t>באיו לאפורש (לואיזיאנה)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mitchellville (S.C.)</t>
+          <t>Lafourche, Bayou (La.)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>987007480256305171</t>
+          <t>987007543967105171</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>32.46167, -80.99222</t>
+          <t>32.12194, -91.96806</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>41.66722, -93.36028</t>
+          <t>30.11164, -90.99372</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1497.8</v>
+        <v>242</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -5147,95 +5497,107 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Q1914731</t>
+          <t>Q2892300</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007543967105171</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007480256305171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>תל סאוואן (עיראק)</t>
+          <t>מפרצון המילטון (ניופאונדלנד ולברדור)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sawwan, Tall (Iraq)</t>
+          <t>Hamilton Inlet (N.L.)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>987007549454405171</t>
+          <t>987007537472705171</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>36.21222, 42.64972</t>
+          <t>54.00000, -57.49806</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>34.11670, 43.90000</t>
+          <t>54.30771, -57.68097</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>259.2</v>
+        <v>36.2</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>no Wikidata entity to arbitrate with</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>5969825</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007537472705171</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007549454405171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>באיו לאפורש (לואיזיאנה)</t>
+          <t>אשנאו (היילברון, גרמניה)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lafourche, Bayou (La.)</t>
+          <t>Eschenau (Heilbronn, Germany)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>987007543967105171</t>
+          <t>987007550227305171</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>32.12194, -91.96806</t>
+          <t>49.13333, 9.40000</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>30.11164, -90.99372</t>
+          <t>49.57428, 11.19847</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>242</v>
+        <v>139.2</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -5249,99 +5611,103 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Q2892300</t>
+          <t>Q62080922</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007550227305171</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007543967105171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>מפרצון המילטון (ניופאונדלנד ולברדור)</t>
+          <t>וייטנאם הדרומית</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hamilton Inlet (N.L.)</t>
+          <t>Vietnam, Southern</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>987007537472705171</t>
+          <t>987007554119405171</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>54.00000, -57.49806</t>
+          <t>11.00000, 107.00000</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>54.30771, -57.68097</t>
+          <t>21.46667, 103.06667</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>36.2</v>
+        <v>1237</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>no Wikidata entity to arbitrate with</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>5969825</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007554119405171</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007537472705171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>אשנאו (היילברון, גרמניה)</t>
+          <t>נהר סלמון (איידהו)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Eschenau (Heilbronn, Germany)</t>
+          <t>Salmon River (Idaho)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>987007550227305171</t>
+          <t>987007553584105171</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>49.13333, 9.40000</t>
+          <t>45.85639, -116.79361</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>49.57428, 11.19847</t>
+          <t>44.57490, -114.49600</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>139.2</v>
+        <v>229.5</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -5350,51 +5716,55 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Q62080922</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>6139605</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007553584105171</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007550227305171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>וייטנאם הדרומית</t>
+          <t>אתר בני חסן (מצרים)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vietnam, Southern</t>
+          <t>Banī Ḥasan Site (Egypt)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>987007554119405171</t>
+          <t>987007551513105171</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>11.00000, 107.00000</t>
+          <t>30.90000, 31.68333</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>21.46667, 103.06667</t>
+          <t>27.93139, 30.87528</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1237</v>
+        <v>339.2</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -5409,41 +5779,45 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007551513105171</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007554119405171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>נהר סלמון (איידהו)</t>
+          <t>נהר מינו (ספרד ופורטוגל)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Salmon River (Idaho)</t>
+          <t>Miño River (Spain and Portugal)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>987007553584105171</t>
+          <t>987007529996605171</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>45.85639, -116.79361</t>
+          <t>41.86667, -8.85000</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>44.57490, -114.49600</t>
+          <t>43.21139, -7.28111</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>229.5</v>
+        <v>197.2</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5452,51 +5826,55 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Q14554</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>6139605</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007529996605171</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007553584105171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>אתר בני חסן (מצרים)</t>
+          <t>קאדור (איטליה)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Banī Ḥasan Site (Egypt)</t>
+          <t>Cadore (Italy)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>987007551513105171</t>
+          <t>987007566295205171</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>30.90000, 31.68333</t>
+          <t>46.50917, 12.35722</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>27.93139, 30.87528</t>
+          <t>45.72222, 11.65762</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>339.2</v>
+        <v>102.8</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5508,44 +5886,52 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Q18505996</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007566295205171</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007551513105171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>נהר מינו (ספרד ופורטוגל)</t>
+          <t>הויבך (באדן-וירטמברג, גרמניה)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Miño River (Spain and Portugal)</t>
+          <t>Heubach (Baden-Württemberg, Germany)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>987007529996605171</t>
+          <t>987007564639705171</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>41.86667, -8.85000</t>
+          <t>51.80000, 7.25000</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>43.21139, -7.28111</t>
+          <t>48.78333, 9.93333</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>197.2</v>
+        <v>385.8</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5559,46 +5945,54 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Q14554</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+          <t>Q326437</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2905154</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564639705171</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007529996605171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>קאדור (איטליה)</t>
+          <t>היספניולה</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cadore (Italy)</t>
+          <t>Hispaniola</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>987007566295205171</t>
+          <t>987007560553605171</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>46.50917, 12.35722</t>
+          <t>-62.66361, -60.38139</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>45.72222, 11.65762</t>
+          <t>19.00000, -71.00000</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>102.8</v>
+        <v>9128.4</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5607,51 +6001,55 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Q18505996</t>
+          <t>Q25277</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007560553605171</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007566295205171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>הויבך (באדן-וירטמברג, גרמניה)</t>
+          <t>חצי האי מלוויל (נונאווט)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Heubach (Baden-Württemberg, Germany)</t>
+          <t>Melville Peninsula (Nunavut)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>987007564639705171</t>
+          <t>987007566381305171</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>51.80000, 7.25000</t>
+          <t>67.50000, -84.00000</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>48.78333, 9.93333</t>
+          <t>68.00097, -83.99891</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>385.8</v>
+        <v>55.7</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5665,50 +6063,54 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Q326437</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2905154</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
+          <t>Q1352266</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>6071994</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007566381305171</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564639705171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>היספניולה</t>
+          <t>בניאס (עיר קדומה) (ישראל)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Hispaniola</t>
+          <t>Banias (Extinct city) (Israel)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>987007560553605171</t>
+          <t>987007554831505171</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-62.66361, -60.38139</t>
+          <t>35.18222, 35.94028</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>19.00000, -71.00000</t>
+          <t>33.24861, 35.69444</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>9128.4</v>
+        <v>216.2</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5722,46 +6124,50 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Q25277</t>
+          <t>Q606295</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007554831505171</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007560553605171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>חצי האי מלוויל (נונאווט)</t>
+          <t>בוקובינה (רומניה ואוקראינה)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Melville Peninsula (Nunavut)</t>
+          <t>Bukovina (Romania and Ukraine)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>987007566381305171</t>
+          <t>987007534359505171</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>67.50000, -84.00000</t>
+          <t>47.77670, 22.87199</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>68.00097, -83.99891</t>
+          <t>48.00000, 26.00000</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>55.7</v>
+        <v>234.5</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -5775,50 +6181,54 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Q1352266</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>6071994</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
+          <t>Q105206</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>571096</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007534359505171</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007566381305171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>בניאס (עיר קדומה) (ישראל)</t>
+          <t>בירוביג'אן (רוסיה)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Banias (Extinct city) (Israel)</t>
+          <t>Birobidzhan (Russia)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>987007554831505171</t>
+          <t>987007554968405171</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>35.18222, 35.94028</t>
+          <t>49.80000, 132.95000</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>33.24861, 35.69444</t>
+          <t>48.78333, 132.93333</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>216.2</v>
+        <v>113.1</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -5832,46 +6242,54 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Q606295</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+          <t>Q7769</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026643</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007554968405171</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007554831505171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>בוקובינה (רומניה ואוקראינה)</t>
+          <t>מונטפיאסקונה (איטליה)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bukovina (Romania and Ukraine)</t>
+          <t>Montefiascone (Italy)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>987007534359505171</t>
+          <t>987007564957105171</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>47.77670, 22.87199</t>
+          <t>42.53957, 12.51957</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>48.00000, 26.00000</t>
+          <t>42.53333, 12.03333</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>234.5</v>
+        <v>39.8</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -5885,107 +6303,111 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Q105206</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>571096</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+          <t>Q176142</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>3172931</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564957105171</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007534359505171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>בירוביג'אן (רוסיה)</t>
+          <t>קיליקיה</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Birobidzhan (Russia)</t>
+          <t>Cilicia</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>987007554968405171</t>
+          <t>987007562363005171</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>49.80000, 132.95000</t>
+          <t>-44.36667, 168.51667</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>48.78333, 132.93333</t>
+          <t>36.98500, 35.12000</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>113.1</v>
+        <v>16055.5</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Q7769</t>
+          <t>Q31651596</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>2026643</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007562363005171</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007554968405171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>מונטפיאסקונה (איטליה)</t>
+          <t>גליפולי (איטליה)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Montefiascone (Italy)</t>
+          <t>Gallipoli (Italy)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>987007564957105171</t>
+          <t>987007562365105171</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>42.53957, 12.51957</t>
+          <t>40.54587, 18.06820</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>42.53333, 12.03333</t>
+          <t>40.05556, 17.99167</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>39.8</v>
+        <v>54.9</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -5999,103 +6421,111 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Q176142</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>3172931</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
+          <t>Q52143</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>11886622</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007562365105171</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564957105171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>קיליקיה</t>
+          <t>איי מריאנה</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cilicia</t>
+          <t>Mariana Islands</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>987007562363005171</t>
+          <t>987007562324405171</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-44.36667, 168.51667</t>
+          <t>16.13333, 145.75000</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>36.98500, 35.12000</t>
+          <t>16.70000, 145.78000</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>16055.5</v>
+        <v>63.1</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Q31651596</t>
+          <t>Q153732</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007562324405171</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007562363005171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>גליפולי (איטליה)</t>
+          <t>וילוויז' (לגניצה, פולין)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Gallipoli (Italy)</t>
+          <t>Wielowieś (Legnica, Poland)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>987007562365105171</t>
+          <t>987007560013405171</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>40.54587, 18.06820</t>
+          <t>51.33598, 16.36796</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>40.05556, 17.99167</t>
+          <t>51.76670, 17.35000</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>54.9</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6109,50 +6539,50 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Q52143</t>
+          <t>Q7999090</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>11886622</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007560013405171</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007562365105171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>איי מריאנה</t>
+          <t>בורבק (אסן, גרמניה)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mariana Islands</t>
+          <t>Borbeck (Essen, Germany)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>987007562324405171</t>
+          <t>987007564629705171</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>16.13333, 145.75000</t>
+          <t>51.48333, 6.95000</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>16.70000, 145.78000</t>
+          <t>53.20583, 8.14806</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>63.1</v>
+        <v>208.1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -6166,46 +6596,50 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Q153732</t>
+          <t>Q15107863</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564629705171</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007562324405171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>וילוויז' (לגניצה, פולין)</t>
+          <t>קודי (אינדונזיה)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wielowieś (Legnica, Poland)</t>
+          <t>Kodi (Indonesia)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>987007560013405171</t>
+          <t>987007564905705171</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>51.33598, 16.36796</t>
+          <t>-33.00000, 118.98333</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>51.76670, 17.35000</t>
+          <t>-9.59270, 118.98559</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>83.09999999999999</v>
+        <v>2602.8</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6219,99 +6653,111 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Q7999090</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
+          <t>Q2451145</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>627127</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564905705171</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007560013405171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>בורבק (אסן, גרמניה)</t>
+          <t>אוברשופהיים (גרמניה)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Borbeck (Essen, Germany)</t>
+          <t>Oberschopfheim (Germany)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>987007564629705171</t>
+          <t>987007567706405171</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>51.48333, 6.95000</t>
+          <t>26.00000, 7.90000</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>53.20583, 8.14806</t>
+          <t>48.39675, 7.90280</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>208.1</v>
+        <v>2490.4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Q15107863</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2859099</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007567706405171</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564629705171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>קודי (אינדונזיה)</t>
+          <t>גרמפיאן (סקוטלנד)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kodi (Indonesia)</t>
+          <t>Grampian (Scotland)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>987007564905705171</t>
+          <t>987007561908705171</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-33.00000, 118.98333</t>
+          <t>57.26667, 3.16667</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>-9.59270, 118.98559</t>
+          <t>57.26667, -3.16667</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2602.8</v>
+        <v>380.7</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -6320,108 +6766,112 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Q2451145</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>627127</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2648228</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007561908705171</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564905705171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>אוברשופהיים (גרמניה)</t>
+          <t>יונאן שנג (סין)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Oberschopfheim (Germany)</t>
+          <t>Yunnan Sheng (China)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>987007567706405171</t>
+          <t>987007564562205171</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>26.00000, 7.90000</t>
+          <t>31.40000, 121.40000</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>48.39675, 7.90280</t>
+          <t>25.04944, 102.70889</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2490.4</v>
+        <v>1959.3</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Q43194</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>2859099</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564562205171</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567706405171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>גרמפיאן (סקוטלנד)</t>
+          <t>בלמונטה קלברו (איטליה)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Grampian (Scotland)</t>
+          <t>Belmonte Calabro (Italy)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>987007561908705171</t>
+          <t>987007564560905171</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>57.26667, 3.16667</t>
+          <t>39.16398, 16.82145</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>57.26667, -3.16667</t>
+          <t>39.16667, 16.08333</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>380.7</v>
+        <v>63.6</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -6430,104 +6880,116 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>2648228</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Q53835</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2525574</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564560905171</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007561908705171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>יונאן שנג (סין)</t>
+          <t>ווטרלו (אונטריו)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Yunnan Sheng (China)</t>
+          <t>Waterloo (Ont.)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>987007564562205171</t>
+          <t>987007564605705171</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>31.40000, 121.40000</t>
+          <t>43.47970, -80.54110</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>25.04944, 102.70889</t>
+          <t>50.71469, 4.39910</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1959.3</v>
+        <v>6119.3</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Q43194</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2783985</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564605705171</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564562205171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>בלמונטה קלברו (איטליה)</t>
+          <t>סטז'יז'וב (מחוז התת-קרפטיים, פולין)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Belmonte Calabro (Italy)</t>
+          <t>Strzyżów (Województwo Podkarpackie, Poland)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>987007564560905171</t>
+          <t>987007564939605171</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>39.16398, 16.82145</t>
+          <t>50.35766, 22.41229</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>39.16667, 16.08333</t>
+          <t>49.87083, 21.79111</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>63.6</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -6541,331 +7003,355 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Q53835</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>2525574</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
+          <t>Q835423</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>757957</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564939605171</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564560905171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ווטרלו (אונטריו)</t>
+          <t>בוליבר (קולומביה : מחוז)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Waterloo (Ont.)</t>
+          <t>Bolívar (Colombia : Department)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>987007564605705171</t>
+          <t>987007564339005171</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>43.47970, -80.54110</t>
+          <t>-17.96667, -66.53333</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>50.71469, 4.39910</t>
+          <t>8.88333, -74.31667</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>6119.3</v>
+        <v>3105.5</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Q230597</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>2783985</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564339005171</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564605705171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>סטז'יז'וב (מחוז התת-קרפטיים, פולין)</t>
+          <t>ורז'ם גרנדה (ברזיל)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Strzyżów (Województwo Podkarpackie, Poland)</t>
+          <t>Vargem Grande (Brazil)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>987007564939605171</t>
+          <t>987007564873205171</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>50.35766, 22.41229</t>
+          <t>-8.83333, -42.50000</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>49.87083, 21.79111</t>
+          <t>-3.54306, -43.91583</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>69.90000000000001</v>
+        <v>608.7</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Wikidata agrees with neither point</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Q835423</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
+          <t>Q22014977</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>3476725</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>757957</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
+          <t>-3.54306, -43.91583 הן הקואורדינטות הנכון (ראו ויקידאטה)</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564873205171</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564939605171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>בוליבר (קולומביה : מחוז)</t>
+          <t>סולון (צרפת)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bolívar (Colombia : Department)</t>
+          <t>Sologne (France)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>987007564339005171</t>
+          <t>987007567019805171</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-17.96667, -66.53333</t>
+          <t>47.83333, 3.00000</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>8.88333, -74.31667</t>
+          <t>47.83333, 2.00000</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3105.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>no Wikidata entity to arbitrate with</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Q230597</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2974334</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>הסולן הוא מדרום ללואר</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007567019805171</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564339005171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ורז'ם גרנדה (ברזיל)</t>
+          <t>שופרונקיהידה (הונגריה)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Vargem Grande (Brazil)</t>
+          <t>Sopronkőhida (Hungary)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>987007564873205171</t>
+          <t>987007562299405171</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-8.83333, -42.50000</t>
+          <t>47.73333, 18.63333</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>-3.54306, -43.91583</t>
+          <t>47.72317, 16.62178</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>608.7</v>
+        <v>150.5</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Wikidata agrees with neither point</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Q22014977</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>3476725</t>
-        </is>
-      </c>
+          <t>Q718321</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>3049576</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-3.54306, -43.91583 הן הקואורדינטות הנכון (ראו ויקידאטה)</t>
+          <t>https://www.nli.org.il/he/authorities/987007562299405171</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564873205171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>סולון (צרפת)</t>
+          <t>שבווה (תימן : פרובינציה)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sologne (France)</t>
+          <t>Shabwah (Yemen : Province)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>987007567019805171</t>
+          <t>987007567130205171</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>47.83333, 3.00000</t>
+          <t>15.00000, 47.00000</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>47.83333, 2.00000</t>
+          <t>16.15306, 43.18667</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>74.59999999999999</v>
+        <v>428.1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>no Wikidata entity to arbitrate with</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Q20308083</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>2974334</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>הסולן הוא מדרום ללואר</t>
+          <t>https://www.nli.org.il/he/authorities/987007567130205171</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567019805171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>שופרונקיהידה (הונגריה)</t>
+          <t>אמפלאקיה (יוון)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sopronkőhida (Hungary)</t>
+          <t>Ampelakia (Greece)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>987007562299405171</t>
+          <t>987007566950505171</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>47.73333, 18.63333</t>
+          <t>39.85000, 22.55000</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>47.72317, 16.62178</t>
+          <t>40.93061, 25.36914</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>150.5</v>
+        <v>267.3</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -6879,315 +7365,339 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Q718321</t>
+          <t>Q21405391</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>3049576</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007566950505171</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007562299405171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>שבווה (תימן : פרובינציה)</t>
+          <t>ליקיה</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Shabwah (Yemen : Province)</t>
+          <t>Lycia</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>987007567130205171</t>
+          <t>987007562204705171</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>15.00000, 47.00000</t>
+          <t>35.05000, 28.75000</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>16.15306, 43.18667</t>
+          <t>36.73333, 29.90000</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>428.1</v>
+        <v>213.9</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Q20308083</t>
+          <t>Q3268401</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007562204705171</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567130205171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>אמפלאקיה (יוון)</t>
+          <t>חסקוי (איסטנבול, טורקיה)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ampelakia (Greece)</t>
+          <t>Hasköy (Istanbul, Turkey)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>987007566950505171</t>
+          <t>987007583688105171</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>39.85000, 22.55000</t>
+          <t>41.38263, 28.95166</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>40.93061, 25.36914</t>
+          <t>41.03972, 28.94972</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>267.3</v>
+        <v>38.1</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Q21405391</t>
+          <t>Q1011290</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007583688105171</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007566950505171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ליקיה</t>
+          <t>מוט (מרסין אילי, טורקיה)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Lycia</t>
+          <t>Mut (Mersin İli, Turkey)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>987007562204705171</t>
+          <t>987007560132205171</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>35.05000, 28.75000</t>
+          <t>36.65000, 32.45000</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>36.73333, 29.90000</t>
+          <t>36.64583, 33.43750</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>213.9</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Q3268401</t>
+          <t>Q94637</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007560132205171</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007562204705171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>חסקוי (איסטנבול, טורקיה)</t>
+          <t>סרוצק (ורשה, פולין)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hasköy (Istanbul, Turkey)</t>
+          <t>Serock (Warsaw, Poland)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>987007583688105171</t>
+          <t>987007560004305171</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>41.38263, 28.95166</t>
+          <t>52.24667, 21.54659</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>41.03972, 28.94972</t>
+          <t>52.51306, 21.06944</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>38.1</v>
+        <v>43.9</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Q1011290</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
+          <t>Q569838</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>759470</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007560004305171</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007583688105171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>מוט (מרסין אילי, טורקיה)</t>
+          <t>פטרובקה (רוסיה : רפובליקה)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mut (Mersin İli, Turkey)</t>
+          <t>Petrovka (R.S.F.S.R.)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>987007560132205171</t>
+          <t>987007562383005171</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>36.65000, 32.45000</t>
+          <t>60.83333, 28.83333</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>36.64583, 33.43750</t>
+          <t>57.19083, 83.92639</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>88.09999999999999</v>
+        <v>3085.2</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>no Wikidata entity to arbitrate with</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Q94637</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>1495080</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007562383005171</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007560132205171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>סרוצק (ורשה, פולין)</t>
+          <t>פרובינציה מזרח בריטניה החדש (פפואה גינאה החדשה)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Serock (Warsaw, Poland)</t>
+          <t>East New Britain Province (Papua New Guinea)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>987007560004305171</t>
+          <t>987007567509405171</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>52.24667, 21.54659</t>
+          <t>-6.50000, 152.50000</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>52.51306, 21.06944</t>
+          <t>-4.61283, 151.88775</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>43.9</v>
+        <v>220.5</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -7196,108 +7706,112 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Q569838</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>759470</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2097853</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007567509405171</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007560004305171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>פטרובקה (רוסיה : רפובליקה)</t>
+          <t>פארצ'ב (לובלין, פולין)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Petrovka (R.S.F.S.R.)</t>
+          <t>Parczew (Lublin, Poland)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>987007562383005171</t>
+          <t>987007567513705171</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>60.83333, 28.83333</t>
+          <t>52.30738, 23.43160</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>57.19083, 83.92639</t>
+          <t>51.63333, 22.86667</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3085.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>no Wikidata entity to arbitrate with</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Q2343396</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>1495080</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007567513705171</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007562383005171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>פרובינציה מזרח בריטניה החדש (פפואה גינאה החדשה)</t>
+          <t>הורודלה (פולין)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>East New Britain Province (Papua New Guinea)</t>
+          <t>Horodło (Poland)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>987007567509405171</t>
+          <t>987007559990305171</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-6.50000, 152.50000</t>
+          <t>50.89437, 24.73120</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>-4.61283, 151.88775</t>
+          <t>50.88333, 24.03333</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>220.5</v>
+        <v>49</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -7306,51 +7820,55 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Q934815</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>2097853</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007559990305171</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567509405171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>פארצ'ב (לובלין, פולין)</t>
+          <t>בכר (אלג'יריה)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Parczew (Lublin, Poland)</t>
+          <t>Béchar (Algeria)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>987007567513705171</t>
+          <t>987007567374905171</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>52.30738, 23.43160</t>
+          <t>31.81499, -1.87823</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>51.63333, 22.86667</t>
+          <t>31.63333, -2.20000</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>84.40000000000001</v>
+        <v>36.5</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -7364,46 +7882,54 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Q2343396</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr"/>
+          <t>Q638704</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>6296382</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007567374905171</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567513705171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>הורודלה (פולין)</t>
+          <t>ארביל (עיראק)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Horodło (Poland)</t>
+          <t>Erbil (Iraq)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>987007559990305171</t>
+          <t>987007564435605171</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>50.89437, 24.73120</t>
+          <t>36.36908, 44.55924</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>50.88333, 24.03333</t>
+          <t>36.19111, 44.00944</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>49</v>
+        <v>53.1</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -7417,46 +7943,50 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Q934815</t>
+          <t>Q132754</t>
         </is>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564435605171</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007559990305171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>בכר (אלג'יריה)</t>
+          <t>חנטשין (מחוז שוויינטוקז'יסקיה, פולין)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Béchar (Algeria)</t>
+          <t>Chęciny (Województwo Świętokrzyskie, Poland)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>987007567374905171</t>
+          <t>987007564539905171</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>31.81499, -1.87823</t>
+          <t>50.81128, 20.46710</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>31.63333, -2.20000</t>
+          <t>51.86833, 21.74556</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>36.5</v>
+        <v>147.3</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -7470,50 +8000,50 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Q638704</t>
+          <t>Q928099</t>
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>6296382</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564539905171</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567374905171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ארביל (עיראק)</t>
+          <t>טרנקוזו (ברזיל)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Erbil (Iraq)</t>
+          <t>Trancoso (Brazil)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>987007564435605171</t>
+          <t>987007567226805171</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>36.36908, 44.55924</t>
+          <t>40.78330, -7.35000</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>36.19111, 44.00944</t>
+          <t>-16.59056, -39.09583</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>53.1</v>
+        <v>7171.5</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -7527,46 +8057,50 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Q132754</t>
+          <t>Q938536</t>
         </is>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007567226805171</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564435605171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>חנטשין (מחוז שוויינטוקז'יסקיה, פולין)</t>
+          <t>מאיקאמר (גרמניה)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Chęciny (Województwo Świętokrzyskie, Poland)</t>
+          <t>Maikammer (Germany)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>987007564539905171</t>
+          <t>987007566958205171</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>50.81128, 20.46710</t>
+          <t>48.30000, 8.13333</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>51.86833, 21.74556</t>
+          <t>49.30471, 8.12527</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>147.3</v>
+        <v>111.7</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -7575,51 +8109,55 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Q928099</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>6555203</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007566958205171</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564539905171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>טרנקוזו (ברזיל)</t>
+          <t>איים איוניים (יוון)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Trancoso (Brazil)</t>
+          <t>Ionian Islands (Greece)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>987007567226805171</t>
+          <t>987007560546705171</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>40.78330, -7.35000</t>
+          <t>38.50000, 20.50000</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>-16.59056, -39.09583</t>
+          <t>37.80000, 20.70000</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>7171.5</v>
+        <v>79.8</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -7633,50 +8171,58 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Q938536</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr"/>
+          <t>Q170295</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>6697805</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007560546705171</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567226805171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>מאיקאמר (גרמניה)</t>
+          <t>סמרנג (אינדונזיה)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Maikammer (Germany)</t>
+          <t>Semarang (Indonesia)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>987007566958205171</t>
+          <t>987007564323305171</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>48.30000, 8.13333</t>
+          <t>-3.78945, 102.29781</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>49.30471, 8.12527</t>
+          <t>-6.99000, 110.42250</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>111.7</v>
+        <v>967.2</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7684,378 +8230,402 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>6555203</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Q13544450</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1627896</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564323305171</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007566958205171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>איים איוניים (יוון)</t>
+          <t>נג'ומבה (טנזניה)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ionian Islands (Greece)</t>
+          <t>Njombe (Tanzania)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>987007560546705171</t>
+          <t>987007562661405171</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>38.50000, 20.50000</t>
+          <t>-90.33333, 34.76667</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>37.80000, 20.70000</t>
+          <t>-9.41667, 34.75000</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>79.8</v>
+        <v>8997.5</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Q170295</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>6697805</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>8469241</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007562661405171</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007560546705171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>סמרנג (אינדונזיה)</t>
+          <t>ג'דידה (מרוקו)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Semarang (Indonesia)</t>
+          <t>Jadīdah (Morocco)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>987007564323305171</t>
+          <t>987007561813405171</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-3.78945, 102.29781</t>
+          <t>33.53106, -7.67457</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>-6.99000, 110.42250</t>
+          <t>33.23420, -8.52280</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>967.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Q13544450</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>1627896</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr"/>
+          <t>Q219583</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>105510</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007561813405171</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564323305171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>נג'ומבה (טנזניה)</t>
+          <t>אנז'ו (צרפת)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Njombe (Tanzania)</t>
+          <t>Anjou (France)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>987007562661405171</t>
+          <t>987007564668505171</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-90.33333, 34.76667</t>
+          <t>45.35000, 4.88333</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>-9.41667, 34.75000</t>
+          <t>47.46667, -0.55000</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>8997.5</v>
+        <v>478.3</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Q107426</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>8469241</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564668505171</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007562661405171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ג'דידה (מרוקו)</t>
+          <t>מניקה (מוזמביק : פרובינציה)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Jadīdah (Morocco)</t>
+          <t>Manica (Mozambique : Province)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>987007561813405171</t>
+          <t>987007567544605171</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>33.53106, -7.67457</t>
+          <t>-18.93444, 32.87556</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>33.23420, -8.52280</t>
+          <t>-19.50000, 33.25000</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>85.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Q219583</t>
+          <t>Q383170</t>
         </is>
       </c>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>105510</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007567544605171</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007561813405171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>אנז'ו (צרפת)</t>
+          <t>בארי (סומליה)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Anjou (France)</t>
+          <t>Bari (Somalia)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>987007564668505171</t>
+          <t>987007567541105171</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>45.35000, 4.88333</t>
+          <t>26.63000, 77.62000</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>47.46667, -0.55000</t>
+          <t>10.83333, 50.18333</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>478.3</v>
+        <v>3368.2</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Q107426</t>
+          <t>Q707848</t>
         </is>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007567541105171</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564668505171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>מניקה (מוזמביק : פרובינציה)</t>
+          <t>בריל (באדן-וירטמברג, גרמניה)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Manica (Mozambique : Province)</t>
+          <t>Brühl (Baden-Württemberg, Germany)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>987007567544605171</t>
+          <t>987007561828205171</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-18.93444, 32.87556</t>
+          <t>49.40000, 8.53333</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>-19.50000, 33.25000</t>
+          <t>50.36210, 9.64677</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>74.2</v>
+        <v>133.4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Q383170</t>
+          <t>Q996914</t>
         </is>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007561828205171</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567544605171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>בארי (סומליה)</t>
+          <t>גנגס (צרפת)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bari (Somalia)</t>
+          <t>Ganges (France)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>987007567541105171</t>
+          <t>987007567552405171</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>26.63000, 77.62000</t>
+          <t>22.08330, 90.83330</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>10.83333, 50.18333</t>
+          <t>43.93417, 3.70833</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3368.2</v>
+        <v>8104.2</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -8069,46 +8639,50 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Q707848</t>
+          <t>Q5089</t>
         </is>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007567552405171</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567541105171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>בריל (באדן-וירטמברג, גרמניה)</t>
+          <t>חאסקובו (בולגריה)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Brühl (Baden-Württemberg, Germany)</t>
+          <t>Khaskovo (Bulgaria)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>987007561828205171</t>
+          <t>987007561902705171</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>49.40000, 8.53333</t>
+          <t>41.76302, 25.89925</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>50.36210, 9.64677</t>
+          <t>41.93465, 25.55556</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>133.4</v>
+        <v>34.3</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -8122,99 +8696,111 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Q996914</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr"/>
+          <t>Q186254</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>730435</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007561902705171</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007561828205171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>גנגס (צרפת)</t>
+          <t>האורה (הודו)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ganges (France)</t>
+          <t>Hāora (India)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>987007567552405171</t>
+          <t>987007564798905171</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>22.08330, 90.83330</t>
+          <t>22.62140, 88.30433</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>43.93417, 3.70833</t>
+          <t>23.38642, 87.51565</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>8104.2</v>
+        <v>117.3</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Q5089</t>
+          <t>Q60817046</t>
         </is>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564798905171</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567552405171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>חאסקובו (בולגריה)</t>
+          <t>קרוביה (פולין)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Khaskovo (Bulgaria)</t>
+          <t>Krobia (Leszno, Poland)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>987007561902705171</t>
+          <t>987007567354305171</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>41.76302, 25.89925</t>
+          <t>51.84406, 16.57560</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>41.93465, 25.55556</t>
+          <t>51.77500, 16.98333</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>34.3</v>
+        <v>29.1</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -8223,55 +8809,55 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Q186254</t>
+          <t>Q556944</t>
         </is>
       </c>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>730435</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007567354305171</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007561902705171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>האורה (הודו)</t>
+          <t>רדין (בלארוס)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Hāora (India)</t>
+          <t>Radunʹ (Belarus)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>987007564798905171</t>
+          <t>987007560358905171</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>22.62140, 88.30433</t>
+          <t>53.45410, 26.36187</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>23.38642, 87.51565</t>
+          <t>54.05306, 24.99778</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>117.3</v>
+        <v>111.7</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -8285,46 +8871,50 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Q60817046</t>
+          <t>Q2995176</t>
         </is>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007560358905171</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564798905171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>קרוביה (פולין)</t>
+          <t>סלנגינסק (רוסיה)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Krobia (Leszno, Poland)</t>
+          <t>Selenginsk (Russia)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>987007567354305171</t>
+          <t>987007564660405171</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>51.84406, 16.57560</t>
+          <t>51.10000, 106.61667</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>51.77500, 16.98333</t>
+          <t>52.00639, 106.86472</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>29.1</v>
+        <v>102.2</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -8336,101 +8926,109 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Q556944</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2017059</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564660405171</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007567354305171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>רדין (בלארוס)</t>
+          <t>אייזן (צ'ילה : פרובינציה)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Radunʹ (Belarus)</t>
+          <t>Aisén (Chile : Province)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>987007560358905171</t>
+          <t>987007564309205171</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>53.45410, 26.36187</t>
+          <t>-45.40000, -72.70000</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>54.05306, 24.99778</t>
+          <t>-44.91667, -73.58333</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>111.7</v>
+        <v>87.7</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Q2995176</t>
+          <t>Q3651</t>
         </is>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564309205171</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007560358905171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>סלנגינסק (רוסיה)</t>
+          <t>סרנאנו (איטליה)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Selenginsk (Russia)</t>
+          <t>Sarnano (Italy)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>987007564660405171</t>
+          <t>987007600144505171</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>51.10000, 106.61667</t>
+          <t>43.34529, 13.29807</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>52.00639, 106.86472</t>
+          <t>43.03475, 13.29818</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>102.2</v>
+        <v>34.5</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -8443,47 +9041,51 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>2017059</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>3167119</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007600144505171</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564660405171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>אייזן (צ'ילה : פרובינציה)</t>
+          <t>מונדזיוב (פולין)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Aisén (Chile : Province)</t>
+          <t>Modrzejów (Poland)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>987007564309205171</t>
+          <t>987007498936105171</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>-45.40000, -72.70000</t>
+          <t>51.26670, 21.25000</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>-44.91667, -73.58333</t>
+          <t>50.24110, 19.14970</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>87.7</v>
+        <v>186.6</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -8497,50 +9099,58 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Q3651</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr"/>
+          <t>Q767989</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>3091543</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007498936105171</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007564309205171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>סרנאנו (איטליה)</t>
+          <t>אלפורד (סקוטלנד : פאריש)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sarnano (Italy)</t>
+          <t>Alford (Scotland : Parish)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>987007600144505171</t>
+          <t>987007480078105171</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>43.34529, 13.29807</t>
+          <t>53.26000, 0.18000</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>43.03475, 13.29818</t>
+          <t>57.22560, -2.73196</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>34.5</v>
+        <v>477.9</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -8548,48 +9158,52 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Q1876378</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>3167119</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007480078105171</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007600144505171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>מונדזיוב (פולין)</t>
+          <t>לטרון (ישראל)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Modrzejów (Poland)</t>
+          <t>Latrun (Israel)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>987007498936105171</t>
+          <t>987007557401105171</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>51.26670, 21.25000</t>
+          <t>33.19538, 35.41241</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>50.24110, 19.14970</t>
+          <t>31.83556, 34.98028</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>186.6</v>
+        <v>156.5</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -8603,482 +9217,408 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Q767989</t>
+          <t>Q681554</t>
         </is>
       </c>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>3091543</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007557401105171</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007498936105171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>אלפורד (סקוטלנד : פאריש)</t>
+          <t>מערת עמוד (ישראל)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Alford (Scotland : Parish)</t>
+          <t>Ammud Cave (Israel)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>987007480078105171</t>
+          <t>987007465731605171</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>53.26000, 0.18000</t>
+          <t>32.86667, 35.50000</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>57.22560, -2.73196</t>
+          <t>32.94588, 35.29633</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>477.9</v>
+        <v>21</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Wikidata backs Kima's point; NLI's stands alone</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Q1876378</t>
+          <t>Q481397</t>
         </is>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007465731605171</t>
+        </is>
+      </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007480078105171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>לטרון (ישראל)</t>
+          <t>וינצנהיים (צרפת)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Latrun (Israel)</t>
+          <t>Wintzenheim (France)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>987007557401105171</t>
+          <t>987007484748005171</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>33.19538, 35.41241</t>
+          <t>48.62737, 7.27563</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>31.83556, 34.98028</t>
+          <t>48.07306, 7.29000</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>156.5</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Q681554</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr"/>
+        <v>61.6</v>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2967337</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007484748005171</t>
+        </is>
+      </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007557401105171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>מערת עמוד (ישראל)</t>
+          <t>טייבורן (לונדון, אנגליה)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ammud Cave (Israel)</t>
+          <t>Tyburn (London, England)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>987007465731605171</t>
+          <t>987007469730505171</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>32.86667, 35.50000</t>
+          <t>52.51667, -1.81667</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>32.94588, 35.29633</t>
+          <t>51.51286, -0.16400</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>21</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>Q481397</t>
-        </is>
-      </c>
+        <v>158.9</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007469730505171</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007465731605171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>וינצנהיים (צרפת)</t>
+          <t>טרנטו (איטליה)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Wintzenheim (France)</t>
+          <t>Trento (Italy)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>987007484748005171</t>
+          <t>987007550224705171</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>48.62737, 7.27563</t>
+          <t>46.20705, 11.49247</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>48.07306, 7.29000</t>
+          <t>46.06667, 11.11667</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>61.6</v>
+        <v>32.9</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>2967337</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007550224705171</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007484748005171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>טייבורן (לונדון, אנגליה)</t>
+          <t>פאקו שיאן (סין)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Tyburn (London, England)</t>
+          <t>Faku Xian (China)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>987007469730505171</t>
+          <t>987007540299505171</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>52.51667, -1.81667</t>
+          <t>42.38333, 123.20000</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>51.51286, -0.16400</t>
+          <t>42.50136, 123.40838</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>158.9</v>
+        <v>21.6</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007540299505171</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007469730505171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>טרנטו (איטליה)</t>
+          <t>מאלאבר (הודו)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Trento (Italy)</t>
+          <t>Malabar (India)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>987007550224705171</t>
+          <t>987007542867205171</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>46.20705, 11.49247</t>
+          <t>19.17908, 72.93791</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>46.06667, 11.11667</t>
+          <t>12.01670, 75.28330</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>32.9</v>
+        <v>835</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>1636747</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007542867205171</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007550224705171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>פאקו שיאן (סין)</t>
+          <t>לואן שי (סין)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Faku Xian (China)</t>
+          <t>Lu'an Shi (China)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>987007540299505171</t>
+          <t>987007540547905171</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>42.38333, 123.20000</t>
+          <t>31.72028, 116.29917</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>42.50136, 123.40838</t>
+          <t>31.75425, 116.50778</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>21.6</v>
+        <v>20.1</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007540547905171</t>
+        </is>
+      </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007540299505171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>מאלאבר (הודו)</t>
+          <t>גורז' (רומניה)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Malabar (India)</t>
+          <t>Gorj (Romania)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>987007542867205171</t>
+          <t>987007548034005171</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>19.17908, 72.93791</t>
+          <t>45.91667, 23.41667</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>12.01670, 75.28330</t>
+          <t>45.04636, 23.28278</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>835</v>
+        <v>97.3</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>1636747</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr"/>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>676898</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007548034005171</t>
+        </is>
+      </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007542867205171</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>לואן שי (סין)</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Lu'an Shi (China)</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>987007540547905171</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>31.72028, 116.29917</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>31.75425, 116.50778</t>
-        </is>
-      </c>
-      <c r="F108" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007540547905171</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>גורז' (רומניה)</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Gorj (Romania)</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>987007548034005171</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>45.91667, 23.41667</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>45.04636, 23.28278</t>
-        </is>
-      </c>
-      <c r="F109" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>676898</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007548034005171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M109"/>
+  <autoFilter ref="A1:M107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9095,8 +9635,8 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9117,12 +9657,12 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>הערת הסוקר</t>
+          <t>קישור לרשומה</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>קישור לרשומה</t>
+          <t>נכלל בדוח מיום</t>
         </is>
       </c>
     </row>
@@ -9142,10 +9682,14 @@
           <t>987012654573505171</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987012654573505171</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987012654573505171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9177,6 +9721,7 @@
     <col width="70" customWidth="1" min="11" max="11"/>
     <col width="52" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9245,6 +9790,11 @@
           <t>קישור לרשומה</t>
         </is>
       </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>נכלל בדוח מיום</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9308,6 +9858,11 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007562429505171</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -9363,6 +9918,11 @@
           <t>https://www.nli.org.il/he/authorities/987007543674705171</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9418,6 +9978,11 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007561549805171</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -9473,6 +10038,11 @@
           <t>https://www.nli.org.il/he/authorities/987007546333605171</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9522,6 +10092,11 @@
           <t>https://www.nli.org.il/he/authorities/987007284646705171</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9575,6 +10150,11 @@
           <t>https://www.nli.org.il/he/authorities/987007564769205171</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9628,6 +10208,11 @@
           <t>https://www.nli.org.il/he/authorities/987011433524905171</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9677,9 +10262,14 @@
           <t>https://www.nli.org.il/he/authorities/987007545173905171</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:N9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9690,7 +10280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9700,6 +10290,7 @@
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9738,6 +10329,11 @@
           <t>קישור לרשומה</t>
         </is>
       </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>נכלל בדוח מיום</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9771,6 +10367,11 @@
           <t>https://www.nli.org.il/he/authorities/987007552593705171</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9808,6 +10409,11 @@
           <t>https://www.nli.org.il/he/authorities/987007559626405171</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9843,6 +10449,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007284075505171</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -9878,9 +10489,14 @@
           <t>https://www.nli.org.il/he/authorities/987007562247105171</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:H5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9891,7 +10507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9901,6 +10517,7 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9939,6 +10556,11 @@
           <t>קישור לרשומה</t>
         </is>
       </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>נכלל בדוח מיום</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9976,6 +10598,11 @@
           <t>https://www.nli.org.il/he/authorities/987013405241405171</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10013,6 +10640,11 @@
           <t>https://www.nli.org.il/he/authorities/987007567653605171</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10050,6 +10682,11 @@
           <t>https://www.nli.org.il/he/authorities/987007469750605171</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10083,9 +10720,14 @@
           <t>https://www.nli.org.il/he/authorities/987007496754305171</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:H5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10096,7 +10738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10109,6 +10751,7 @@
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10162,6 +10805,11 @@
           <t>קישור לשנייה</t>
         </is>
       </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>נכלל בדוח מיום</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10208,6 +10856,11 @@
           <t>https://www.nli.org.il/he/authorities/987007552849305171</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10252,6 +10905,11 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007542743705171</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -10298,6 +10956,11 @@
           <t>https://www.nli.org.il/he/authorities/987007555268305171</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10342,6 +11005,11 @@
           <t>https://www.nli.org.il/he/authorities/987007477335005171</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10390,6 +11058,11 @@
       <c r="J6" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007566710505171</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -10420,9 +11093,14 @@
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J7"/>
+  <autoFilter ref="A1:K7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10446,9 +11124,9 @@
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="52" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10504,17 +11182,17 @@
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>לבדיקה לפני שליחה</t>
+          <t>הערת הסוקר</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>הערת הסוקר</t>
+          <t>קישור לרשומה</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>קישור לרשומה</t>
+          <t>נכלל בדוח מיום</t>
         </is>
       </c>
     </row>
@@ -10566,10 +11244,14 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987011060395805171</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987011060395805171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -10615,10 +11297,14 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007562214205171</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007562214205171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -10672,10 +11358,14 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007494092005171</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007494092005171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -10729,10 +11419,14 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007545176905171</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007545176905171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -10785,15 +11479,19 @@
           <t>לפי הערת הסוקר, הרשומה הנכנסת היא Lubin שבפולין — השם העכשווי — ו־Lüben/Lueben הם וריאנטים היסטוריים שלה. הרשומה השנייה היא Lübben שבברנדנבורג (Q584815). שני מקומות שונים ב־170 ק״מ.</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>צריך להיות Lubin (Dolnośląskie, Poland)  - השם העכשווי. luben כמו גם Lueben צריכים להיות וריאנטים.</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>צריך להיות Lubin (Dolnośląskie, Poland)  - השם העכשווי. luben כמו גם Lueben צריכים להיות וריאנטים.</t>
+          <t>https://www.nli.org.il/he/authorities/987007494367505171</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007494367505171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -10828,15 +11526,19 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>לצורך דיסאמביגואציה של השם בעברית. לחלופין, אפשר להוסיף מחוזות (מונטגומרי, פרנקלין), אם כי מריון סטיישן הוא השם המוכר יותר.</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>לצורך דיסאמביגואציה של השם בעברית. לחלופין, אפשר להוסיף מחוזות (מונטגומרי, פרנקלין), אם כי מריון סטיישן הוא השם המוכר יותר.</t>
+          <t>https://www.nli.org.il/he/authorities/987007559599105171</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007559599105171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -10872,10 +11574,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987010489292905171</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987010489292905171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -10911,10 +11617,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987011252608705171</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987011252608705171</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>

--- a/nli-report.xlsx
+++ b/nli-report.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'אפס שנשמט'!$A$1:$K$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'קואורדינטות שגויות'!$A$1:$M$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'034 פגום'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'מזהה ויקינתונים'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'מזהה ויקינתונים'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'תיקון הכותרת'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'זהות הכותרת'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'כפילות ברשומות'!$A$1:$K$7</definedName>
@@ -9705,7 +9705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9718,10 +9718,9 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="70" customWidth="1" min="11" max="11"/>
-    <col width="52" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9777,20 +9776,15 @@
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>פירוט הממצא הנוסף</t>
+          <t>הערת הסוקר</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>הערת הסוקר</t>
+          <t>קישור לרשומה</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>קישור לרשומה</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>נכלל בדוח מיום</t>
         </is>
@@ -9852,15 +9846,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>בעיה בשם הערבי</t>
+          <t>https://www.nli.org.il/he/authorities/987007562429505171</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007562429505171</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9912,13 +9901,12 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007543674705171</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007543674705171</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9969,18 +9957,17 @@
         <v>104.5</v>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>אלה הם שני מקומות שונים: העיר וההר. אם הכוונה לעיר, הויקידאטה הוא Q651583 והשם: הויקידאטה והקואורדינטות הנוכחיות ב-nli הן לא של etters-berg אלא של ettersburg הישוב. אם הכוונה היא להר, ממליצה לשנות את השם לאטרס-ברג (גרמניה: הר) והויקידאטה הוא  Q31547753</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>אלה הם שני מקומות שונים: העיר וההר. אם הכוונה לעיר, הויקידאטה הוא Q651583 והשם: הויקידאטה והקואורדינטות הנוכחיות ב-nli הן לא של etters-berg אלא של ettersburg הישוב. אם הכוונה היא להר, ממליצה לשנות את השם לאטרס-ברג (גרמניה: הר) והויקידאטה הוא  Q31547753</t>
+          <t>https://www.nli.org.il/he/authorities/987007561549805171</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007561549805171</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10032,13 +10019,12 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007546333605171</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007546333605171</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10086,13 +10072,12 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007284646705171</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007284646705171</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10144,13 +10129,12 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564769205171</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007564769205171</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10202,13 +10186,12 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987011433524905171</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987011433524905171</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10256,20 +10239,19 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007545173905171</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007545173905171</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
           <t>2026-09-22</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N9"/>
+  <autoFilter ref="A1:M9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/nli-report.xlsx
+++ b/nli-report.xlsx
@@ -20,13 +20,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'אפס שנשמט'!$A$1:$K$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'קואורדינטות שגויות'!$A$1:$M$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'קואורדינטות שגויות'!$A$1:$K$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'034 פגום'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'מזהה ויקינתונים'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'מזהה ויקינתונים'!$A$1:$L$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'תיקון הכותרת'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'זהות הכותרת'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'כפילות ברשומות'!$A$1:$K$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'כותרת לשני מקומות'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'כותרת לשני מקומות'!$A$1:$K$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -948,7 +948,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>להוסיף מבחין לכותרת העברית של כל אחד מן הצדדים. העמודות "הצעה לרשומה הנכנסת" ו"הצעה לרשומה הקיימת" נושאות הצעה קונקרטית לכל צד. ההצעות המסומנות "טיוטה" הן הצעות שלנו ולא הכרעה — הן נסמכות על החלוקה המנהלית בוויקינתונים, ואנו מבקשים את דעתכם עליהן.</t>
+          <t>להוסיף מבחין לכותרת העברית של כל אחד מן הצדדים. העמודות "הצעה לרשומה הנכנסת" ו"הצעה לרשומה הקיימת" נושאות הצעה קונקרטית לכל צד. ההצעות הן הצעות שלנו ולא הכרעה — הן נסמכות על החלוקה המנהלית בוויקינתונים, ואנו מבקשים את דעתכם עליהן.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M107"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3459,13 +3459,11 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col hidden="1" width="34" customWidth="1" min="7" max="7"/>
-    <col hidden="1" width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="52" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3501,35 +3499,25 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>סוג הממצא</t>
+          <t>ויקינתונים ברשומה</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>ביטחון</t>
+          <t>GeoNames</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>ויקינתונים ברשומה</t>
+          <t>הערת הסוקר</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>GeoNames</t>
+          <t>קישור לרשומה</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>הערת הסוקר</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>קישור לרשומה</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>נכלל בדוח מיום</t>
         </is>
@@ -3566,31 +3554,21 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q2416499</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Q2416499</t>
-        </is>
-      </c>
+          <t>2822902</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2822902</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007507581905171</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -3627,31 +3605,21 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q1893589</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Q1893589</t>
-        </is>
-      </c>
+          <t>7532897</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7532897</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007522876305171</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -3688,31 +3656,21 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Q10107</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Q10107</t>
-        </is>
-      </c>
+          <t>5140907</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5140907</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007290978605171</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -3749,31 +3707,21 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q34696004</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Q34696004</t>
-        </is>
-      </c>
+          <t>4674406</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4674406</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007534295705171</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -3810,27 +3758,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
           <t>Q1111219</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007561062905171</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -3867,31 +3805,21 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>river/region/range — both points lie on the feature, no real move</t>
+          <t>Q1544388</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Q1544388</t>
-        </is>
-      </c>
+          <t>5549209</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5549209</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007551287205171</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -3928,27 +3856,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
           <t>Q2777355</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007565185505171</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -3983,25 +3901,15 @@
       <c r="F9" t="n">
         <v>275.8</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987012219373405171</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4038,31 +3946,21 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q2865</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Q2865</t>
-        </is>
-      </c>
+          <t>2892518</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2892518</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007564322205171</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4099,27 +3997,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
           <t>Q125309</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007284803205171</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4156,31 +4044,21 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q940488</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Q940488</t>
-        </is>
-      </c>
+          <t>4368319</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4368319</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007529708805171</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4217,27 +4095,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
           <t>Q41642</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007555456905171</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4274,27 +4142,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
           <t>Q190571</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007415889605171</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4331,27 +4189,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
           <t>Q12707</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007540907105171</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4386,29 +4234,19 @@
       <c r="F16" t="n">
         <v>333.9</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2692969</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2692969</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007552629505171</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4445,27 +4283,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
           <t>Q1464482</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007554238205171</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4500,25 +4328,15 @@
       <c r="F18" t="n">
         <v>51.1</v>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007282291905171</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4555,27 +4373,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
           <t>Q5349602</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007524670705171</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4612,31 +4420,21 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q995940</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Q995940</t>
-        </is>
-      </c>
+          <t>2943520</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2943520</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007507433105171</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4673,31 +4471,21 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q166966</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Q166966</t>
-        </is>
-      </c>
+          <t>143160</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>143160</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007536434705171</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4734,35 +4522,25 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Q4821258</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>741074</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Q4821258</t>
+          <t>יש הרבה מקומות בשם זה בטורקיה - במקרה הזה מזהה הויקידאטה לא תואם את הקואורדינטות.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>741074</t>
+          <t>https://www.nli.org.il/he/authorities/987007583811505171</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
-        <is>
-          <t>יש הרבה מקומות בשם זה בטורקיה - במקרה הזה מזהה הויקידאטה לא תואם את הקואורדינטות.</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007583811505171</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4799,27 +4577,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
           <t>Q14452</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007567857705171</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4856,27 +4624,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
           <t>Q27468</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007560192505171</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4911,25 +4669,15 @@
       <c r="F25" t="n">
         <v>326.2</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007294887505171</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4966,31 +4714,21 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q51930</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Q51930</t>
-        </is>
-      </c>
+          <t>3165250</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>3165250</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007541762605171</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5025,25 +4763,15 @@
       <c r="F27" t="n">
         <v>160</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007536002505171</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5080,31 +4808,21 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q4831991</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Q4831991</t>
-        </is>
-      </c>
+          <t>312116</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>312116</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007537927405171</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5141,27 +4859,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
           <t>Q5584067</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007539410905171</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5198,31 +4906,21 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q18456541</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Q18456541</t>
-        </is>
-      </c>
+          <t>8953134</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>8953134</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007550230005171</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5257,29 +4955,19 @@
       <c r="F31" t="n">
         <v>3263.9</v>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>no Wikidata entity to arbitrate with</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>3013637</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3013637</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007535425005171</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5316,31 +5004,21 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q255416</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Q255416</t>
-        </is>
-      </c>
+          <t>6291043</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>6291043</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007489333905171</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5377,27 +5055,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
           <t>Q1914731</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007480256305171</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5432,25 +5100,15 @@
       <c r="F34" t="n">
         <v>259.2</v>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007549454405171</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5487,27 +5145,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
           <t>Q2892300</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007543967105171</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5542,29 +5190,19 @@
       <c r="F36" t="n">
         <v>36.2</v>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>no Wikidata entity to arbitrate with</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>5969825</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>5969825</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007537472705171</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5601,27 +5239,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
           <t>Q62080922</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007550227305171</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5656,25 +5284,15 @@
       <c r="F38" t="n">
         <v>1237</v>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007554119405171</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5709,29 +5327,19 @@
       <c r="F39" t="n">
         <v>229.5</v>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>6139605</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>6139605</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007553584105171</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5766,25 +5374,15 @@
       <c r="F40" t="n">
         <v>339.2</v>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007551513105171</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5821,27 +5419,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
           <t>Q14554</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007529996605171</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5878,27 +5466,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
           <t>Q18505996</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007566295205171</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5935,31 +5513,21 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q326437</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Q326437</t>
-        </is>
-      </c>
+          <t>2905154</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2905154</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007564639705171</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5996,27 +5564,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
           <t>Q25277</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007560553605171</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6053,31 +5611,21 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q1352266</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Q1352266</t>
-        </is>
-      </c>
+          <t>6071994</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>6071994</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007566381305171</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6114,27 +5662,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
           <t>Q606295</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007554831505171</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6171,31 +5709,21 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q105206</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Q105206</t>
-        </is>
-      </c>
+          <t>571096</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>571096</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007534359505171</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6232,31 +5760,21 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q7769</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Q7769</t>
-        </is>
-      </c>
+          <t>2026643</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026643</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007554968405171</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6293,31 +5811,21 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q176142</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Q176142</t>
-        </is>
-      </c>
+          <t>3172931</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3172931</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007564957105171</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6354,27 +5862,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
           <t>Q31651596</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007562363005171</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6411,31 +5909,21 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q52143</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Q52143</t>
-        </is>
-      </c>
+          <t>11886622</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>11886622</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007562365105171</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6472,27 +5960,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
           <t>Q153732</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007562324405171</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6529,27 +6007,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
           <t>Q7999090</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007560013405171</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6586,27 +6054,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
           <t>Q15107863</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007564629705171</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6643,31 +6101,21 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q2451145</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Q2451145</t>
-        </is>
-      </c>
+          <t>627127</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>627127</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007564905705171</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6702,29 +6150,19 @@
       <c r="F56" t="n">
         <v>2490.4</v>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2859099</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2859099</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007567706405171</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6759,29 +6197,19 @@
       <c r="F57" t="n">
         <v>380.7</v>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2648228</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2648228</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007561908705171</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6818,27 +6246,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
           <t>Q43194</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007564562205171</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6875,31 +6293,21 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q53835</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Q53835</t>
-        </is>
-      </c>
+          <t>2525574</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2525574</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007564560905171</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6934,29 +6342,19 @@
       <c r="F60" t="n">
         <v>6119.3</v>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2783985</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2783985</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007564605705171</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6993,31 +6391,21 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q835423</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Q835423</t>
-        </is>
-      </c>
+          <t>757957</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>757957</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007564939605171</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7054,27 +6442,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
           <t>Q230597</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr">
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007564339005171</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7111,35 +6489,25 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Wikidata agrees with neither point</t>
+          <t>Q22014977</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>3476725</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Q22014977</t>
+          <t>-3.54306, -43.91583 הן הקואורדינטות הנכונות (ראו ויקידאטה)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>3476725</t>
+          <t>https://www.nli.org.il/he/authorities/987007564873205171</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
-        <is>
-          <t>-3.54306, -43.91583 הן הקואורדינטות הנכון (ראו ויקידאטה)</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007564873205171</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7174,33 +6542,23 @@
       <c r="F64" t="n">
         <v>74.59999999999999</v>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>no Wikidata entity to arbitrate with</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>2974334</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>אזור הסולון מוגדר כאזור שמדרום ללואר</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2974334</t>
+          <t>https://www.nli.org.il/he/authorities/987007567019805171</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
-        <is>
-          <t>הסולן הוא מדרום ללואר</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007567019805171</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7237,31 +6595,21 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q718321</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Q718321</t>
-        </is>
-      </c>
+          <t>3049576</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>3049576</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007562299405171</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7298,27 +6646,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
           <t>Q20308083</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007567130205171</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7355,27 +6693,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
           <t>Q21405391</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007566950505171</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7412,27 +6740,17 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
           <t>Q3268401</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007562204705171</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7469,27 +6787,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
           <t>Q1011290</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007583688105171</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7526,27 +6834,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
           <t>Q94637</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007560132205171</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7583,31 +6881,21 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q569838</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Q569838</t>
-        </is>
-      </c>
+          <t>759470</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>759470</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007560004305171</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7642,29 +6930,19 @@
       <c r="F72" t="n">
         <v>3085.2</v>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>no Wikidata entity to arbitrate with</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>1495080</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>1495080</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007562383005171</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7699,29 +6977,19 @@
       <c r="F73" t="n">
         <v>220.5</v>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2097853</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2097853</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007567509405171</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7758,27 +7026,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
           <t>Q2343396</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr">
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007567513705171</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7815,27 +7073,17 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
           <t>Q934815</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr">
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007559990305171</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7872,31 +7120,21 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q638704</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Q638704</t>
-        </is>
-      </c>
+          <t>6296382</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>6296382</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007567374905171</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7933,27 +7171,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
           <t>Q132754</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007564435605171</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7990,27 +7218,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
           <t>Q928099</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr">
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007564539905171</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8047,27 +7265,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
           <t>Q938536</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr">
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007567226805171</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8102,29 +7310,19 @@
       <c r="F80" t="n">
         <v>111.7</v>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>6555203</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>6555203</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007566958205171</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8161,31 +7359,21 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q170295</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Q170295</t>
-        </is>
-      </c>
+          <t>6697805</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>6697805</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007560546705171</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8222,31 +7410,21 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Q13544450</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Q13544450</t>
-        </is>
-      </c>
+          <t>1627896</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>1627896</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007564323305171</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8281,29 +7459,19 @@
       <c r="F83" t="n">
         <v>8997.5</v>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>8469241</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>8469241</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007562661405171</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8340,31 +7508,21 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q219583</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Q219583</t>
-        </is>
-      </c>
+          <t>105510</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>105510</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007561813405171</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8401,27 +7559,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
           <t>Q107426</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr">
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007564668505171</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8458,27 +7606,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
           <t>Q383170</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr">
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007567544605171</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8515,27 +7653,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
           <t>Q707848</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr">
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007567541105171</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8572,27 +7700,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
           <t>Q996914</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr">
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007561828205171</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8629,27 +7747,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
           <t>Q5089</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr">
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007567552405171</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8686,31 +7794,21 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
+          <t>Q186254</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Q186254</t>
-        </is>
-      </c>
+          <t>730435</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>730435</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007561902705171</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8747,27 +7845,17 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
           <t>Q60817046</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr">
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007564798905171</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8804,27 +7892,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
           <t>Q556944</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr">
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007567354305171</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8861,27 +7939,17 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
           <t>Q2995176</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr">
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007560358905171</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8916,29 +7984,19 @@
       <c r="F94" t="n">
         <v>102.2</v>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2017059</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2017059</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007564660405171</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8975,27 +8033,17 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
           <t>Q3651</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr">
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007564309205171</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9030,29 +8078,19 @@
       <c r="F96" t="n">
         <v>34.5</v>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>3167119</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
-          <t>3167119</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007600144505171</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9089,31 +8127,21 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
+          <t>Q767989</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Q767989</t>
-        </is>
-      </c>
+          <t>3091543</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
-          <t>3091543</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007498936105171</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9150,27 +8178,17 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
           <t>Q1876378</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr">
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007480078105171</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9207,27 +8225,17 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Kima is bound to a same-named place elsewhere — a link error, not a move</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
           <t>Q681554</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr">
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007557401105171</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9264,27 +8272,17 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Wikidata backs Kima's point; NLI's stands alone</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
           <t>Q481397</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr">
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007465731605171</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9320,20 +8318,18 @@
         <v>61.6</v>
       </c>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2967337</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2967337</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007484748005171</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9371,14 +8367,12 @@
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007469730505171</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr">
+      <c r="K102" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9416,14 +8410,12 @@
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007550224705171</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9461,14 +8453,12 @@
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007540299505171</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9504,20 +8494,18 @@
         <v>835</v>
       </c>
       <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>1636747</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>1636747</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007542867205171</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9555,14 +8543,12 @@
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007540547905171</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9598,27 +8584,25 @@
         <v>97.3</v>
       </c>
       <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>676898</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>676898</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007548034005171</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M107"/>
+  <autoFilter ref="A1:K107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9705,7 +8689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9717,10 +8701,9 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="52" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9771,20 +8754,15 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>ממצא נוסף</t>
+          <t>הערת הסוקר</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>הערת הסוקר</t>
+          <t>קישור לרשומה</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>קישור לרשומה</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>נכלל בדוח מיום</t>
         </is>
@@ -9836,20 +8814,15 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>שם ערבי משובש</t>
+          <t>הכותרת הערבית ברשומה היא "لوخفيت︠س︡ي︠ي︠ي︠ي︠ي︠ي (أوكرانيا)" — האות ي חוזרת שמונה פעמים. מקור התקלה בתעתיק: הצורה הלטינית Lokhvyt︠s︡i︠a︡ משתמשת בסימני חיבור (U+FE20/U+FE21) כדי לקשור t͡s ו־i͡a, וההמרה לערבית התייחסה לכל חצי סימן כאל אות ולכן שכפלה את ي. הצורה המוצעת: "لوخفيتسيا (أوكرانيا)". זו תקלה בודדת — אחת מתוך 1,188 כותרות ערביות שנבדקו.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>הכותרת הערבית ברשומה היא "لوخفيت︠س︡ي︠ي︠ي︠ي︠ي︠ي (أوكرانيا)" — האות ي חוזרת שמונה פעמים. מקור התקלה בתעתיק: הצורה הלטינית Lokhvyt︠s︡i︠a︡ משתמשת בסימני חיבור (U+FE20/U+FE21) כדי לקשור t͡s ו־i͡a, וההמרה לערבית התייחסה לכל חצי סימן כאל אות ולכן שכפלה את ي. הצורה המוצעת: "لوخفيتسيا (أوكرانيا)". זו תקלה בודדת — אחת מתוך 1,188 כותרות ערביות שנבדקו.</t>
+          <t>https://www.nli.org.il/he/authorities/987007562429505171</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007562429505171</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9900,13 +8873,12 @@
         <v>2797.7</v>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007543674705171</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007543674705171</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9956,18 +8928,17 @@
       <c r="I4" t="n">
         <v>104.5</v>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>אלה הם שני מקומות שונים: העיר וההר. אם הכוונה לעיר, הויקידאטה הוא Q651583 והשם: הויקידאטה והקואורדינטות הנוכחיות ב-nli הן לא של etters-berg אלא של ettersburg הישוב. אם הכוונה היא להר, ממליצה לשנות את השם לאטרס-ברג (גרמניה: הר) והויקידאטה הוא  Q31547753</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>אלה הם שני מקומות שונים: העיר וההר. אם הכוונה לעיר, הויקידאטה הוא Q651583 והשם: הויקידאטה והקואורדינטות הנוכחיות ב-nli הן לא של etters-berg אלא של ettersburg הישוב. אם הכוונה היא להר, ממליצה לשנות את השם לאטרס-ברג (גרמניה: הר) והויקידאטה הוא  Q31547753</t>
+          <t>https://www.nli.org.il/he/authorities/987007561549805171</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007561549805171</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10018,13 +8989,12 @@
         <v>54.8</v>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007546333605171</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007546333605171</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10071,13 +9041,12 @@
         <v>149.4</v>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007284646705171</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007284646705171</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10128,13 +9097,12 @@
         <v>852.1</v>
       </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007564769205171</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007564769205171</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10185,13 +9153,12 @@
         <v>726.9</v>
       </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987011433524905171</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987011433524905171</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10238,20 +9205,19 @@
         <v>141.3</v>
       </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007545173905171</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://www.nli.org.il/he/authorities/987007545173905171</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
           <t>2026-09-22</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:L9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10341,7 +9307,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>אין כאן שגיאת איות אלא שאלת זהות: יש שטרסבורג גרמנית (Q565624) השונה מזו הצרפתית של היום. האם יש צורך לשמר את הזהות הזו? אם כן, מוטב להוסיף 1871-1918 לכותרת הראשית.</t>
+          <t>אין כאן שגיאת איות אלא שאלת זהות: יש מקום בגרמניה העכשווית בשם שטרסבורג (Q565624) והוא שונה מזו הצרפתית של היום. אם הכוונה אליו, יש להוריד את ההערה הקושרת בין השניים ומומלץ להוסיף מבחין (אוקרמארק, גרמניה) שיבהיר זאת. אם הכוונה לשטרסבורג שכיום בצרפת, מוטב להוסיף 1871-1918 לכותרת הראשית.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -10383,7 +9349,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>האיות העברי אינו תואם את Ingolstadt.</t>
+          <t>האיות העברי אינו תואם את Ingolstadt. חסרה נ׳.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -10425,7 +9391,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cnidus — התעתיק המקובל הוא בקו״ף. כמו כן הסוגר הסופי חסר בכותרת, והרמיזות כוללות את הסוגריים שלא כבדרך כלל.</t>
+          <t>Cnidus — התעתיק המקובל הוא בקו״ף. ר הוא כנראה טעות כתיב. כמו כן הסוגר הסופי חסר בכותרת.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -10572,7 +9538,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>כפילות ב־NLI: שתי רשומות חיות לאותו כפר — 987007547821005171 (Planes, Spain) ו־987013405241405171 (Planes (Spain)). שתיהן נושאות פלאנס (ספרד) בעברית. לדווח לספרייה. בכימה: לתקן את כותרת 76207 מ־'פליינס, ספרד' ל־'פלאנס (ספרד)' — פליינס היא שגיאת קריאה (Plains האנגלי במקום Planes הספרדי; ההשראה כנראה פליינס (ג'ורג'יה)/Plains (Ga.)). להפנות ל־987013405241405171 ולהוסיף Q1983306. פליינס אינה וריאנט לגיטימי — לכל היותר צורה מוקצית, לא שם חלופי.</t>
+          <t>כפילות ב־NLI: שתי רשומות קיימות לאותו הכפר — 987007547821005171 (Planes, Spain) ו־987013405241405171 (Planes (Spain)). שתיהן נושאות פלאנס (ספרד) בעברית.  פליינס היא שגיאת קריאה (Plains האנגלי במקום Planes הספרדי; ההשראה כנראה פליינס (ג'ורג'יה)/Plains (Ga.)). להפנות ל־987013405241405171 ולהוסיף Q1983306. פליינס אינה אפילו וריאנט לגיטימי.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -10614,7 +9580,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Osterwick הוא רובע ביישוב קטן, לא סביר שאליו הכוונה. הכיתוב הנכון הוא Osterwieck ולכן כדאי לאחד (בכימה) ולדווח כפילות ל-nli</t>
+          <t>Osterwick הוא רובע ביישוב קטן, לא סביר שאליו הכוונה. הכיתוב הנכון הוא Osterwieck ולכן כדאי לאחד את השניים (או לשמור אותם נפרדים ולהוסיף מבחין מחוזי).</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -10656,7 +9622,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>השם העברי של רשומה 987007469750605171</t>
+          <t>טרבזון ניתן בטעות כשם העברי של Ardeşen (Turkey) - רשומת המקום טרבזון כבר קיימת.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -10825,7 +9791,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>sommerville  is wrong. Should be 1 m only.</t>
+          <t>נכתב ב-m אחת. השני נראה טעות.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -11029,7 +9995,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>טולבוחין הוא שם היסטורי של דובריץ׳</t>
+          <t>טולבוחין הוא שם היסטורי של דובריץ׳ וצריך להצטרף כרמיזה.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -11093,22 +10059,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="52" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11119,60 +10083,50 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>מעמד ההצעה</t>
+          <t>הרשומה הנכנסת (לטינית)</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>הרשומה הנכנסת (לטינית)</t>
+          <t>מזהה NLI</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>מזהה NLI</t>
+          <t>הצעה לרשומה הנכנסת</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>הצעה לרשומה הנכנסת</t>
+          <t>הרשומה הקיימת (לטינית)</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>הרשומה הקיימת (לטינית)</t>
+          <t>מזהה הרשומה הקיימת</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>מזהה הרשומה הקיימת</t>
+          <t>הצעה לרשומה הקיימת</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>הצעה לרשומה הקיימת</t>
+          <t>מרחק (ק״מ)</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>מרחק (ק״מ)</t>
+          <t>נימוק ההצעה</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>נימוק ההצעה</t>
+          <t>קישור לרשומה</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>הערת הסוקר</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>קישור לרשומה</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>נכלל בדוח מיום</t>
         </is>
@@ -11186,52 +10140,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>טיוטה</t>
+          <t>Hochstätten (Germany)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hochstätten (Germany)</t>
+          <t>987011060395805171</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>987011060395805171</t>
+          <t>הוכשטטן (באד קרויצנאך, גרמניה)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>הוכשטטן (מחוז באד קרויצנאך, גרמניה)</t>
+          <t>Hochstetten (Germany)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hochstetten (Germany)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
           <t>987007467698905171</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>הוכשטטן (גרמניה)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>שתי רשומות שונות: Hochstätten שבמחוז באד קרויצנאך, ו־Hochstetten באיות אחר. ההצעה מוסיפה את המחוז לרשומה הנכנסת; יש לאשר מהי הרשומה השנייה לפני שמציעים לה מבחין.</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>שתי רשומות שונות: Hochstätten שבמחוז באד קרויצנאך, ו־Hochstetten באיות אחר. ההצעה מוסיפה את המחוז לרשומה הנכנסת; יש לאשר מהי הרשומה השנייה לפני שמציעים לה מבחין.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987011060395805171</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11243,48 +10187,46 @@
           <t>קאבה (הונגריה)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kaba (Hungary)</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kaba (Hungary)</t>
+          <t>987007562214205171</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>987007562214205171</t>
+          <t>קאבה (היידו-ביהר, הונגריה)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>קאבה (היידו-ביהר, הונגריה)</t>
+          <t>Káva (Hungary)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Káva (Hungary)</t>
+          <t>987007373278105171</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>987007373278105171</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
           <t>קאבה (פשט, הונגריה)</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="H3" t="n">
         <v>127.4</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987007562214205171</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11298,54 +10240,48 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>טיוטה</t>
+          <t>Ehningen (Germany)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ehningen (Germany)</t>
+          <t>987007494092005171</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>987007494092005171</t>
+          <t>אנינגן (בלינגן, גרמניה)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>אנינגן (מחוז בבלינגן, גרמניה)</t>
+          <t>Eningen unter Achalm (Germany)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Eningen unter Achalm (Germany)</t>
+          <t>987007557723505171</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>987007557723505171</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>אנינגן אונטר אכלם (מחוז רויטלינגן, גרמניה)</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
+          <t>אנינגן אונטר אכלם (רויטלינגן, גרמניה)</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>31.1</v>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>שני יישובים שונים במרחק 31 ק״מ: Ehningen שבמחוז בבלינגן (Q314758) ו־Eningen unter Achalm שבמחוז רויטלינגן (Q81423). שמות המחוזות לקוחים מתוויות ויקינתונים בעברית.</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>שני יישובים שונים במרחק 31 ק״מ: Ehningen שבמחוז בבלינגן (Q314758) ו־Eningen unter Achalm שבמחוז רויטלינגן (Q81423). שמות המחוזות לקוחים מתוויות ויקינתונים בעברית.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007494092005171</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11359,54 +10295,48 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>טיוטה</t>
+          <t>Cherniïv (Ukraine)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cherniïv (Ukraine)</t>
+          <t>987007545176905171</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>987007545176905171</t>
+          <t>צ'רנייב (איוונו-פרנקיבסק, אוקראינה)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>צ'רנייב (מחוז איוונו-פרנקיבסק, אוקראינה)</t>
+          <t>Chernihiv (Ukraine)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chernihiv (Ukraine)</t>
+          <t>987007566754005171</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>987007566754005171</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
           <t>צ'רניהיב (אוקראינה)</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="H5" t="n">
         <v>552.8</v>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>כאן לא די במבחין: המרחק 553 ק״מ, והרשומה השנייה היא צ׳רניהיב — בירת המחוז (Q157053), שהתעתיק העברי המקובל לה בוויקינתונים הוא "צ׳רניהיב" ולא "צ׳רנייב". כלומר אחת הכותרות שגויה ולא רק עמומה.</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>כאן לא די במבחין: המרחק 553 ק״מ, והרשומה השנייה היא צ׳רניהיב — בירת המחוז (Q157053), שהתעתיק העברי המקובל לה בוויקינתונים הוא "צ׳רניהיב" ולא "צ׳רנייב". כלומר אחת הכותרות שגויה ולא רק עמומה.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
           <t>https://www.nli.org.il/he/authorities/987007545176905171</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11420,58 +10350,48 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>טיוטה</t>
+          <t>Lüben (Germany)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lüben (Germany)</t>
+          <t>987007494367505171</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>987007494367505171</t>
+          <t>לובין (דולנוסלונסקיה, פולין)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>לובין (מחוז דולנוסלונסקיה, פולין)</t>
+          <t>Lübben (Germany)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lübben (Germany)</t>
+          <t>987007473617305171</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>987007473617305171</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>לובן (מחוז דאמה-שפרוואלד, גרמניה)</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+          <t>לובן (דאמה-שפרוואלד, גרמניה)</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>170</v>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>צריך להיות Lubin (Dolnośląskie, Poland)  - השם העכשווי. luben כמו גם Lueben צריכים להיות וריאנטים. הרשומה השנייה היא Lübben שבברנדנבורג (Q584815).</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>לפי הערת הסוקר, הרשומה הנכנסת היא Lubin שבפולין — השם העכשווי — ו־Lüben/Lueben הם וריאנטים היסטוריים שלה. הרשומה השנייה היא Lübben שבברנדנבורג (Q584815). שני מקומות שונים ב־170 ק״מ.</t>
+          <t>https://www.nli.org.il/he/authorities/987007494367505171</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
-        <is>
-          <t>צריך להיות Lubin (Dolnośląskie, Poland)  - השם העכשווי. luben כמו גם Lueben צריכים להיות וריאנטים.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007494367505171</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11483,42 +10403,40 @@
           <t>מריון (פנסילבניה)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Merion (Pa.)</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Merion (Pa.)</t>
+          <t>987007559599105171</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>987007559599105171</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
           <t>מריון סטיישן (פנסילבניה)</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>מריון (פנסילבניה)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>לחלופין, אפשר להוסיף לצורך ההבחנה את שמות המחוזות (מונטגומרי, פרנקלין), בכל מקרה מריון סטיישן הוא השם המוכר יותר.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/he/authorities/987007559599105171</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
-        <is>
-          <t>לצורך דיסאמביגואציה של השם בעברית. לחלופין, אפשר להוסיף מחוזות (מונטגומרי, פרנקלין), אם כי מריון סטיישן הוא השם המוכר יותר.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/he/authorities/987007559599105171</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11530,38 +10448,36 @@
           <t>פוליני (צרפת)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pulligny (France)</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pulligny (France)</t>
+          <t>987010489292905171</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>987010489292905171</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>פוליני (מחוז מרת ומוזל, צרפת)</t>
-        </is>
-      </c>
+          <t>פוליני (מרת ומוזל, צרפת)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>פוליני (מחוז יורה, צרפת)</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>פוליני (יורה, צרפת)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987010489292905171</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11573,45 +10489,43 @@
           <t>אופנהיים (גרמניה)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Uffenheim (Germany)</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uffenheim (Germany)</t>
+          <t>987011252608705171</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>987011252608705171</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
           <t>אופנהיים (בוואריה, גרמניה)</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>אופנהיים (ריינלנד-פפאלץ, גרמניה)</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>https://www.nli.org.il/he/authorities/987011252608705171</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:K9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>